--- a/Assets/AddressableResource/Data/Excels/TowerBossLevelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerBossLevelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963A8B25-614B-49CD-B490-F6AC4562F033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868ABDEF-B877-4851-8984-0D72111DD8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -1870,7 +1870,7 @@
         <v>44</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" ref="D24:D52" si="9">D23+15</f>
+        <f t="shared" ref="D24:D32" si="9">D23+15</f>
         <v>165</v>
       </c>
       <c r="E24" s="2">
@@ -2460,7 +2460,7 @@
         <v>64</v>
       </c>
       <c r="D34" s="2">
-        <f t="shared" ref="D34:D52" si="10">D33+27</f>
+        <f t="shared" ref="D34:D51" si="10">D33+27</f>
         <v>339</v>
       </c>
       <c r="E34" s="2">
@@ -8492,7 +8492,7 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
-        <f t="shared" ref="A133:C196" si="36">A132+1</f>
+        <f t="shared" ref="A133:B196" si="36">A132+1</f>
         <v>131</v>
       </c>
       <c r="B133" s="2">
@@ -10648,7 +10648,7 @@
         <v>332</v>
       </c>
       <c r="D168" s="2">
-        <f t="shared" ref="D168:D202" si="41">D167+11</f>
+        <f t="shared" ref="D168:D201" si="41">D167+11</f>
         <v>2391</v>
       </c>
       <c r="E168" s="2">
@@ -12405,7 +12405,7 @@
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" s="7">
-        <f t="shared" ref="A197:C260" si="52">A196+1</f>
+        <f t="shared" ref="A197:B260" si="52">A196+1</f>
         <v>195</v>
       </c>
       <c r="B197" s="2">
@@ -55234,15 +55234,16 @@
         <v>0.35666666666666669</v>
       </c>
       <c r="H902" s="8">
-        <f>(A902-799)*12070</f>
-        <v>1219070</v>
+        <f>(A902-879)*93070</f>
+        <v>1954470</v>
       </c>
       <c r="I902" s="9">
-        <v>25</v>
+        <f>I901+5</f>
+        <v>30</v>
       </c>
       <c r="L902" s="2">
         <f t="shared" si="173"/>
-        <v>1219070</v>
+        <v>1954470</v>
       </c>
       <c r="M902" s="2">
         <f t="shared" si="174"/>
@@ -55258,11 +55259,11 @@
       </c>
       <c r="P902" s="16">
         <f>SUM($H$3:H902)</f>
-        <v>325879010</v>
+        <v>326614410</v>
       </c>
       <c r="Q902" s="2">
         <f>SUM($I$3:I902)</f>
-        <v>12774</v>
+        <v>12779</v>
       </c>
     </row>
     <row r="903" spans="1:17" x14ac:dyDescent="0.3">
@@ -55294,15 +55295,16 @@
         <v>0.35709999999999997</v>
       </c>
       <c r="H903" s="8">
-        <f t="shared" ref="H903:H966" si="183">(A903-799)*12070</f>
-        <v>1231140</v>
+        <f t="shared" ref="H903:H966" si="183">(A903-879)*93070</f>
+        <v>2047540</v>
       </c>
       <c r="I903" s="9">
-        <v>25</v>
+        <f t="shared" ref="I903:I966" si="184">I902+5</f>
+        <v>35</v>
       </c>
       <c r="L903" s="2">
         <f t="shared" si="173"/>
-        <v>1231140</v>
+        <v>2047540</v>
       </c>
       <c r="M903" s="2">
         <f t="shared" si="174"/>
@@ -55318,11 +55320,11 @@
       </c>
       <c r="P903" s="16">
         <f>SUM($H$3:H903)</f>
-        <v>327110150</v>
+        <v>328661950</v>
       </c>
       <c r="Q903" s="2">
         <f>SUM($I$3:I903)</f>
-        <v>12799</v>
+        <v>12814</v>
       </c>
     </row>
     <row r="904" spans="1:17" x14ac:dyDescent="0.3">
@@ -55355,14 +55357,15 @@
       </c>
       <c r="H904" s="8">
         <f t="shared" si="183"/>
-        <v>1243210</v>
+        <v>2140610</v>
       </c>
       <c r="I904" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>40</v>
       </c>
       <c r="L904" s="2">
         <f t="shared" si="173"/>
-        <v>1243210</v>
+        <v>2140610</v>
       </c>
       <c r="M904" s="2">
         <f t="shared" si="174"/>
@@ -55378,11 +55381,11 @@
       </c>
       <c r="P904" s="16">
         <f>SUM($H$3:H904)</f>
-        <v>328353360</v>
+        <v>330802560</v>
       </c>
       <c r="Q904" s="2">
         <f>SUM($I$3:I904)</f>
-        <v>12824</v>
+        <v>12854</v>
       </c>
     </row>
     <row r="905" spans="1:17" x14ac:dyDescent="0.3">
@@ -55415,34 +55418,35 @@
       </c>
       <c r="H905" s="8">
         <f t="shared" si="183"/>
-        <v>1255280</v>
+        <v>2233680</v>
       </c>
       <c r="I905" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>45</v>
       </c>
       <c r="L905" s="2">
-        <f t="shared" ref="L905:L968" si="184">H905</f>
-        <v>1255280</v>
+        <f t="shared" ref="L905:L968" si="185">H905</f>
+        <v>2233680</v>
       </c>
       <c r="M905" s="2">
-        <f t="shared" ref="M905:M968" si="185">B905</f>
+        <f t="shared" ref="M905:M968" si="186">B905</f>
         <v>1253</v>
       </c>
       <c r="N905" s="15">
-        <f t="shared" ref="N905:N968" si="186">C905</f>
+        <f t="shared" ref="N905:N968" si="187">C905</f>
         <v>21265.492455701515</v>
       </c>
       <c r="O905" s="15">
-        <f t="shared" ref="O905:O968" si="187">D905</f>
+        <f t="shared" ref="O905:O968" si="188">D905</f>
         <v>35154.473581955346</v>
       </c>
       <c r="P905" s="16">
         <f>SUM($H$3:H905)</f>
-        <v>329608640</v>
+        <v>333036240</v>
       </c>
       <c r="Q905" s="2">
         <f>SUM($I$3:I905)</f>
-        <v>12849</v>
+        <v>12899</v>
       </c>
     </row>
     <row r="906" spans="1:17" x14ac:dyDescent="0.3">
@@ -55475,34 +55479,35 @@
       </c>
       <c r="H906" s="8">
         <f t="shared" si="183"/>
-        <v>1267350</v>
+        <v>2326750</v>
       </c>
       <c r="I906" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>50</v>
       </c>
       <c r="L906" s="2">
-        <f t="shared" si="184"/>
-        <v>1267350</v>
+        <f t="shared" si="185"/>
+        <v>2326750</v>
       </c>
       <c r="M906" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1254</v>
       </c>
       <c r="N906" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21306.624630934188</v>
       </c>
       <c r="O906" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35227.990923145262</v>
       </c>
       <c r="P906" s="16">
         <f>SUM($H$3:H906)</f>
-        <v>330875990</v>
+        <v>335362990</v>
       </c>
       <c r="Q906" s="2">
         <f>SUM($I$3:I906)</f>
-        <v>12874</v>
+        <v>12949</v>
       </c>
     </row>
     <row r="907" spans="1:17" x14ac:dyDescent="0.3">
@@ -55526,7 +55531,7 @@
         <v>1</v>
       </c>
       <c r="F907" s="2">
-        <f t="shared" ref="F907:F970" si="188">F887+0.2</f>
+        <f t="shared" ref="F907:F970" si="189">F887+0.2</f>
         <v>8.4000000000000021</v>
       </c>
       <c r="G907" s="17">
@@ -55535,34 +55540,35 @@
       </c>
       <c r="H907" s="8">
         <f t="shared" si="183"/>
-        <v>1279420</v>
+        <v>2419820</v>
       </c>
       <c r="I907" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>55</v>
       </c>
       <c r="L907" s="2">
-        <f t="shared" si="184"/>
-        <v>1279420</v>
+        <f t="shared" si="185"/>
+        <v>2419820</v>
       </c>
       <c r="M907" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1255</v>
       </c>
       <c r="N907" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21347.770428353258</v>
       </c>
       <c r="O907" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35301.556967458979</v>
       </c>
       <c r="P907" s="16">
         <f>SUM($H$3:H907)</f>
-        <v>332155410</v>
+        <v>337782810</v>
       </c>
       <c r="Q907" s="2">
         <f>SUM($I$3:I907)</f>
-        <v>12899</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="908" spans="1:17" x14ac:dyDescent="0.3">
@@ -55586,7 +55592,7 @@
         <v>1</v>
       </c>
       <c r="F908" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G908" s="17">
@@ -55595,34 +55601,35 @@
       </c>
       <c r="H908" s="8">
         <f t="shared" si="183"/>
-        <v>1291490</v>
+        <v>2512890</v>
       </c>
       <c r="I908" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>60</v>
       </c>
       <c r="L908" s="2">
-        <f t="shared" si="184"/>
-        <v>1291490</v>
+        <f t="shared" si="185"/>
+        <v>2512890</v>
       </c>
       <c r="M908" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1256</v>
       </c>
       <c r="N908" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21388.929829942892</v>
       </c>
       <c r="O908" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35375.171666579838</v>
       </c>
       <c r="P908" s="16">
         <f>SUM($H$3:H908)</f>
-        <v>333446900</v>
+        <v>340295700</v>
       </c>
       <c r="Q908" s="2">
         <f>SUM($I$3:I908)</f>
-        <v>12924</v>
+        <v>13064</v>
       </c>
     </row>
     <row r="909" spans="1:17" x14ac:dyDescent="0.3">
@@ -55646,7 +55653,7 @@
         <v>1</v>
       </c>
       <c r="F909" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G909" s="17">
@@ -55655,34 +55662,35 @@
       </c>
       <c r="H909" s="8">
         <f t="shared" si="183"/>
-        <v>1303560</v>
+        <v>2605960</v>
       </c>
       <c r="I909" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>65</v>
       </c>
       <c r="L909" s="2">
-        <f t="shared" si="184"/>
-        <v>1303560</v>
+        <f t="shared" si="185"/>
+        <v>2605960</v>
       </c>
       <c r="M909" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1257</v>
       </c>
       <c r="N909" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21430.102817740837</v>
       </c>
       <c r="O909" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35448.834972318873</v>
       </c>
       <c r="P909" s="16">
         <f>SUM($H$3:H909)</f>
-        <v>334750460</v>
+        <v>342901660</v>
       </c>
       <c r="Q909" s="2">
         <f>SUM($I$3:I909)</f>
-        <v>12949</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="910" spans="1:17" x14ac:dyDescent="0.3">
@@ -55706,7 +55714,7 @@
         <v>1</v>
       </c>
       <c r="F910" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G910" s="17">
@@ -55715,34 +55723,35 @@
       </c>
       <c r="H910" s="8">
         <f t="shared" si="183"/>
-        <v>1315630</v>
+        <v>2699030</v>
       </c>
       <c r="I910" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>70</v>
       </c>
       <c r="L910" s="2">
-        <f t="shared" si="184"/>
-        <v>1315630</v>
+        <f t="shared" si="185"/>
+        <v>2699030</v>
       </c>
       <c r="M910" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1258</v>
       </c>
       <c r="N910" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21471.289373838074</v>
       </c>
       <c r="O910" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35522.546836614085</v>
       </c>
       <c r="P910" s="16">
         <f>SUM($H$3:H910)</f>
-        <v>336066090</v>
+        <v>345600690</v>
       </c>
       <c r="Q910" s="2">
         <f>SUM($I$3:I910)</f>
-        <v>12974</v>
+        <v>13199</v>
       </c>
     </row>
     <row r="911" spans="1:17" x14ac:dyDescent="0.3">
@@ -55766,7 +55775,7 @@
         <v>1</v>
       </c>
       <c r="F911" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G911" s="17">
@@ -55775,34 +55784,35 @@
       </c>
       <c r="H911" s="8">
         <f t="shared" si="183"/>
-        <v>1327700</v>
+        <v>2792100</v>
       </c>
       <c r="I911" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>75</v>
       </c>
       <c r="L911" s="2">
-        <f t="shared" si="184"/>
-        <v>1327700</v>
+        <f t="shared" si="185"/>
+        <v>2792100</v>
       </c>
       <c r="M911" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1259</v>
       </c>
       <c r="N911" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21512.489480378597</v>
       </c>
       <c r="O911" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35596.307211530017</v>
       </c>
       <c r="P911" s="16">
         <f>SUM($H$3:H911)</f>
-        <v>337393790</v>
+        <v>348392790</v>
       </c>
       <c r="Q911" s="2">
         <f>SUM($I$3:I911)</f>
-        <v>12999</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="912" spans="1:17" x14ac:dyDescent="0.3">
@@ -55826,7 +55836,7 @@
         <v>1</v>
       </c>
       <c r="F912" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G912" s="17">
@@ -55835,34 +55845,35 @@
       </c>
       <c r="H912" s="8">
         <f t="shared" si="183"/>
-        <v>1339770</v>
+        <v>2885170</v>
       </c>
       <c r="I912" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>80</v>
       </c>
       <c r="L912" s="2">
-        <f t="shared" si="184"/>
-        <v>1339770</v>
+        <f t="shared" si="185"/>
+        <v>2885170</v>
       </c>
       <c r="M912" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1260</v>
       </c>
       <c r="N912" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21553.703119559268</v>
       </c>
       <c r="O912" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35670.116049257318</v>
       </c>
       <c r="P912" s="16">
         <f>SUM($H$3:H912)</f>
-        <v>338733560</v>
+        <v>351277960</v>
       </c>
       <c r="Q912" s="2">
         <f>SUM($I$3:I912)</f>
-        <v>13024</v>
+        <v>13354</v>
       </c>
     </row>
     <row r="913" spans="1:17" x14ac:dyDescent="0.3">
@@ -55886,7 +55897,7 @@
         <v>1</v>
       </c>
       <c r="F913" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G913" s="17">
@@ -55895,34 +55906,35 @@
       </c>
       <c r="H913" s="8">
         <f t="shared" si="183"/>
-        <v>1351840</v>
+        <v>2978240</v>
       </c>
       <c r="I913" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>85</v>
       </c>
       <c r="L913" s="2">
-        <f t="shared" si="184"/>
-        <v>1351840</v>
+        <f t="shared" si="185"/>
+        <v>2978240</v>
       </c>
       <c r="M913" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1261</v>
       </c>
       <c r="N913" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21594.930273629383</v>
       </c>
       <c r="O913" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35743.973302111845</v>
       </c>
       <c r="P913" s="16">
         <f>SUM($H$3:H913)</f>
-        <v>340085400</v>
+        <v>354256200</v>
       </c>
       <c r="Q913" s="2">
         <f>SUM($I$3:I913)</f>
-        <v>13049</v>
+        <v>13439</v>
       </c>
     </row>
     <row r="914" spans="1:17" x14ac:dyDescent="0.3">
@@ -55946,7 +55958,7 @@
         <v>1</v>
       </c>
       <c r="F914" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G914" s="17">
@@ -55955,34 +55967,35 @@
       </c>
       <c r="H914" s="8">
         <f t="shared" si="183"/>
-        <v>1363910</v>
+        <v>3071310</v>
       </c>
       <c r="I914" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>90</v>
       </c>
       <c r="L914" s="2">
-        <f t="shared" si="184"/>
-        <v>1363910</v>
+        <f t="shared" si="185"/>
+        <v>3071310</v>
       </c>
       <c r="M914" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1262</v>
       </c>
       <c r="N914" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21636.170924890608</v>
       </c>
       <c r="O914" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35817.878922534539</v>
       </c>
       <c r="P914" s="16">
         <f>SUM($H$3:H914)</f>
-        <v>341449310</v>
+        <v>357327510</v>
       </c>
       <c r="Q914" s="2">
         <f>SUM($I$3:I914)</f>
-        <v>13074</v>
+        <v>13529</v>
       </c>
     </row>
     <row r="915" spans="1:17" x14ac:dyDescent="0.3">
@@ -56006,7 +56019,7 @@
         <v>1</v>
       </c>
       <c r="F915" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G915" s="17">
@@ -56015,34 +56028,35 @@
       </c>
       <c r="H915" s="8">
         <f t="shared" si="183"/>
-        <v>1375980</v>
+        <v>3164380</v>
       </c>
       <c r="I915" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>95</v>
       </c>
       <c r="L915" s="2">
-        <f t="shared" si="184"/>
-        <v>1375980</v>
+        <f t="shared" si="185"/>
+        <v>3164380</v>
       </c>
       <c r="M915" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1263</v>
       </c>
       <c r="N915" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21677.425055696687</v>
       </c>
       <c r="O915" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35891.832863090684</v>
       </c>
       <c r="P915" s="16">
         <f>SUM($H$3:H915)</f>
-        <v>342825290</v>
+        <v>360491890</v>
       </c>
       <c r="Q915" s="2">
         <f>SUM($I$3:I915)</f>
-        <v>13099</v>
+        <v>13624</v>
       </c>
     </row>
     <row r="916" spans="1:17" x14ac:dyDescent="0.3">
@@ -56066,7 +56080,7 @@
         <v>1</v>
       </c>
       <c r="F916" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G916" s="17">
@@ -56075,34 +56089,35 @@
       </c>
       <c r="H916" s="8">
         <f t="shared" si="183"/>
-        <v>1388050</v>
+        <v>3257450</v>
       </c>
       <c r="I916" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>100</v>
       </c>
       <c r="L916" s="2">
-        <f t="shared" si="184"/>
-        <v>1388050</v>
+        <f t="shared" si="185"/>
+        <v>3257450</v>
       </c>
       <c r="M916" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1264</v>
       </c>
       <c r="N916" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21718.69264845311</v>
       </c>
       <c r="O916" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>35965.835076469411</v>
       </c>
       <c r="P916" s="16">
         <f>SUM($H$3:H916)</f>
-        <v>344213340</v>
+        <v>363749340</v>
       </c>
       <c r="Q916" s="2">
         <f>SUM($I$3:I916)</f>
-        <v>13124</v>
+        <v>13724</v>
       </c>
     </row>
     <row r="917" spans="1:17" x14ac:dyDescent="0.3">
@@ -56126,7 +56141,7 @@
         <v>1</v>
       </c>
       <c r="F917" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G917" s="17">
@@ -56135,34 +56150,35 @@
       </c>
       <c r="H917" s="8">
         <f t="shared" si="183"/>
-        <v>1400120</v>
+        <v>3350520</v>
       </c>
       <c r="I917" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>105</v>
       </c>
       <c r="L917" s="2">
-        <f t="shared" si="184"/>
-        <v>1400120</v>
+        <f t="shared" si="185"/>
+        <v>3350520</v>
       </c>
       <c r="M917" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1265</v>
       </c>
       <c r="N917" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21759.973685617038</v>
       </c>
       <c r="O917" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36039.88551548314</v>
       </c>
       <c r="P917" s="16">
         <f>SUM($H$3:H917)</f>
-        <v>345613460</v>
+        <v>367099860</v>
       </c>
       <c r="Q917" s="2">
         <f>SUM($I$3:I917)</f>
-        <v>13149</v>
+        <v>13829</v>
       </c>
     </row>
     <row r="918" spans="1:17" x14ac:dyDescent="0.3">
@@ -56186,7 +56202,7 @@
         <v>1</v>
       </c>
       <c r="F918" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G918" s="17">
@@ -56195,34 +56211,35 @@
       </c>
       <c r="H918" s="8">
         <f t="shared" si="183"/>
-        <v>1412190</v>
+        <v>3443590</v>
       </c>
       <c r="I918" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>110</v>
       </c>
       <c r="L918" s="2">
-        <f t="shared" si="184"/>
-        <v>1412190</v>
+        <f t="shared" si="185"/>
+        <v>3443590</v>
       </c>
       <c r="M918" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1266</v>
       </c>
       <c r="N918" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21801.268149696956</v>
       </c>
       <c r="O918" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36113.984133067206</v>
       </c>
       <c r="P918" s="16">
         <f>SUM($H$3:H918)</f>
-        <v>347025650</v>
+        <v>370543450</v>
       </c>
       <c r="Q918" s="2">
         <f>SUM($I$3:I918)</f>
-        <v>13174</v>
+        <v>13939</v>
       </c>
     </row>
     <row r="919" spans="1:17" x14ac:dyDescent="0.3">
@@ -56246,7 +56263,7 @@
         <v>1</v>
       </c>
       <c r="F919" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G919" s="17">
@@ -56255,34 +56272,35 @@
       </c>
       <c r="H919" s="8">
         <f t="shared" si="183"/>
-        <v>1424260</v>
+        <v>3536660</v>
       </c>
       <c r="I919" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>115</v>
       </c>
       <c r="L919" s="2">
-        <f t="shared" si="184"/>
-        <v>1424260</v>
+        <f t="shared" si="185"/>
+        <v>3536660</v>
       </c>
       <c r="M919" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1267</v>
       </c>
       <c r="N919" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21842.576023252463</v>
       </c>
       <c r="O919" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36188.130882279074</v>
       </c>
       <c r="P919" s="16">
         <f>SUM($H$3:H919)</f>
-        <v>348449910</v>
+        <v>374080110</v>
       </c>
       <c r="Q919" s="2">
         <f>SUM($I$3:I919)</f>
-        <v>13199</v>
+        <v>14054</v>
       </c>
     </row>
     <row r="920" spans="1:17" x14ac:dyDescent="0.3">
@@ -56306,7 +56324,7 @@
         <v>1</v>
       </c>
       <c r="F920" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G920" s="17">
@@ -56315,34 +56333,35 @@
       </c>
       <c r="H920" s="8">
         <f t="shared" si="183"/>
-        <v>1436330</v>
+        <v>3629730</v>
       </c>
       <c r="I920" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>120</v>
       </c>
       <c r="L920" s="2">
-        <f t="shared" si="184"/>
-        <v>1436330</v>
+        <f t="shared" si="185"/>
+        <v>3629730</v>
       </c>
       <c r="M920" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1268</v>
       </c>
       <c r="N920" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21883.897288894008</v>
       </c>
       <c r="O920" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36262.325716297993</v>
       </c>
       <c r="P920" s="16">
         <f>SUM($H$3:H920)</f>
-        <v>349886240</v>
+        <v>377709840</v>
       </c>
       <c r="Q920" s="2">
         <f>SUM($I$3:I920)</f>
-        <v>13224</v>
+        <v>14174</v>
       </c>
     </row>
     <row r="921" spans="1:17" x14ac:dyDescent="0.3">
@@ -56366,7 +56385,7 @@
         <v>1</v>
       </c>
       <c r="F921" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="G921" s="17">
@@ -56375,34 +56394,35 @@
       </c>
       <c r="H921" s="8">
         <f t="shared" si="183"/>
-        <v>1448400</v>
+        <v>3722800</v>
       </c>
       <c r="I921" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>125</v>
       </c>
       <c r="L921" s="2">
-        <f t="shared" si="184"/>
-        <v>1448400</v>
+        <f t="shared" si="185"/>
+        <v>3722800</v>
       </c>
       <c r="M921" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1269</v>
       </c>
       <c r="N921" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21925.231929282792</v>
       </c>
       <c r="O921" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36336.568588424721</v>
       </c>
       <c r="P921" s="16">
         <f>SUM($H$3:H921)</f>
-        <v>351334640</v>
+        <v>381432640</v>
       </c>
       <c r="Q921" s="2">
         <f>SUM($I$3:I921)</f>
-        <v>13249</v>
+        <v>14299</v>
       </c>
     </row>
     <row r="922" spans="1:17" x14ac:dyDescent="0.3">
@@ -56426,7 +56446,7 @@
         <v>1</v>
       </c>
       <c r="F922" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G922" s="17">
@@ -56435,34 +56455,35 @@
       </c>
       <c r="H922" s="8">
         <f t="shared" si="183"/>
-        <v>1460470</v>
+        <v>3815870</v>
       </c>
       <c r="I922" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>130</v>
       </c>
       <c r="L922" s="2">
-        <f t="shared" si="184"/>
-        <v>1460470</v>
+        <f t="shared" si="185"/>
+        <v>3815870</v>
       </c>
       <c r="M922" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1270</v>
       </c>
       <c r="N922" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>21966.579927130366</v>
       </c>
       <c r="O922" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36410.859452080411</v>
       </c>
       <c r="P922" s="16">
         <f>SUM($H$3:H922)</f>
-        <v>352795110</v>
+        <v>385248510</v>
       </c>
       <c r="Q922" s="2">
         <f>SUM($I$3:I922)</f>
-        <v>13274</v>
+        <v>14429</v>
       </c>
     </row>
     <row r="923" spans="1:17" x14ac:dyDescent="0.3">
@@ -56486,7 +56507,7 @@
         <v>1</v>
       </c>
       <c r="F923" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G923" s="17">
@@ -56495,34 +56516,35 @@
       </c>
       <c r="H923" s="8">
         <f t="shared" si="183"/>
-        <v>1472540</v>
+        <v>3908940</v>
       </c>
       <c r="I923" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>135</v>
       </c>
       <c r="L923" s="2">
-        <f t="shared" si="184"/>
-        <v>1472540</v>
+        <f t="shared" si="185"/>
+        <v>3908940</v>
       </c>
       <c r="M923" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1271</v>
       </c>
       <c r="N923" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22007.941265198471</v>
       </c>
       <c r="O923" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36485.198260806646</v>
       </c>
       <c r="P923" s="16">
         <f>SUM($H$3:H923)</f>
-        <v>354267650</v>
+        <v>389157450</v>
       </c>
       <c r="Q923" s="2">
         <f>SUM($I$3:I923)</f>
-        <v>13299</v>
+        <v>14564</v>
       </c>
     </row>
     <row r="924" spans="1:17" x14ac:dyDescent="0.3">
@@ -56546,7 +56568,7 @@
         <v>1</v>
       </c>
       <c r="F924" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G924" s="17">
@@ -56555,34 +56577,35 @@
       </c>
       <c r="H924" s="8">
         <f t="shared" si="183"/>
-        <v>1484610</v>
+        <v>4002010</v>
       </c>
       <c r="I924" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>140</v>
       </c>
       <c r="L924" s="2">
-        <f t="shared" si="184"/>
-        <v>1484610</v>
+        <f t="shared" si="185"/>
+        <v>4002010</v>
       </c>
       <c r="M924" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1272</v>
       </c>
       <c r="N924" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22049.315926298885</v>
       </c>
       <c r="O924" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36559.584968264782</v>
       </c>
       <c r="P924" s="16">
         <f>SUM($H$3:H924)</f>
-        <v>355752260</v>
+        <v>393159460</v>
       </c>
       <c r="Q924" s="2">
         <f>SUM($I$3:I924)</f>
-        <v>13324</v>
+        <v>14704</v>
       </c>
     </row>
     <row r="925" spans="1:17" x14ac:dyDescent="0.3">
@@ -56606,7 +56629,7 @@
         <v>1</v>
       </c>
       <c r="F925" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G925" s="17">
@@ -56615,34 +56638,35 @@
       </c>
       <c r="H925" s="8">
         <f t="shared" si="183"/>
-        <v>1496680</v>
+        <v>4095080</v>
       </c>
       <c r="I925" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>145</v>
       </c>
       <c r="L925" s="2">
-        <f t="shared" si="184"/>
-        <v>1496680</v>
+        <f t="shared" si="185"/>
+        <v>4095080</v>
       </c>
       <c r="M925" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1273</v>
       </c>
       <c r="N925" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22090.703893293117</v>
       </c>
       <c r="O925" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36634.01952823528</v>
       </c>
       <c r="P925" s="16">
         <f>SUM($H$3:H925)</f>
-        <v>357248940</v>
+        <v>397254540</v>
       </c>
       <c r="Q925" s="2">
         <f>SUM($I$3:I925)</f>
-        <v>13349</v>
+        <v>14849</v>
       </c>
     </row>
     <row r="926" spans="1:17" x14ac:dyDescent="0.3">
@@ -56666,7 +56690,7 @@
         <v>1</v>
       </c>
       <c r="F926" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G926" s="17">
@@ -56675,34 +56699,35 @@
       </c>
       <c r="H926" s="8">
         <f t="shared" si="183"/>
-        <v>1508750</v>
+        <v>4188150</v>
       </c>
       <c r="I926" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>150</v>
       </c>
       <c r="L926" s="2">
-        <f t="shared" si="184"/>
-        <v>1508750</v>
+        <f t="shared" si="185"/>
+        <v>4188150</v>
       </c>
       <c r="M926" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1274</v>
       </c>
       <c r="N926" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22132.105149092185</v>
       </c>
       <c r="O926" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36708.501894617548</v>
       </c>
       <c r="P926" s="16">
         <f>SUM($H$3:H926)</f>
-        <v>358757690</v>
+        <v>401442690</v>
       </c>
       <c r="Q926" s="2">
         <f>SUM($I$3:I926)</f>
-        <v>13374</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="927" spans="1:17" x14ac:dyDescent="0.3">
@@ -56726,7 +56751,7 @@
         <v>1</v>
       </c>
       <c r="F927" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G927" s="17">
@@ -56735,34 +56760,35 @@
       </c>
       <c r="H927" s="8">
         <f t="shared" si="183"/>
-        <v>1520820</v>
+        <v>4281220</v>
       </c>
       <c r="I927" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>155</v>
       </c>
       <c r="L927" s="2">
-        <f t="shared" si="184"/>
-        <v>1520820</v>
+        <f t="shared" si="185"/>
+        <v>4281220</v>
       </c>
       <c r="M927" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1275</v>
       </c>
       <c r="N927" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22173.519676656386</v>
       </c>
       <c r="O927" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36783.03202142896</v>
       </c>
       <c r="P927" s="16">
         <f>SUM($H$3:H927)</f>
-        <v>360278510</v>
+        <v>405723910</v>
       </c>
       <c r="Q927" s="2">
         <f>SUM($I$3:I927)</f>
-        <v>13399</v>
+        <v>15154</v>
       </c>
     </row>
     <row r="928" spans="1:17" x14ac:dyDescent="0.3">
@@ -56786,7 +56812,7 @@
         <v>1</v>
       </c>
       <c r="F928" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G928" s="17">
@@ -56795,34 +56821,35 @@
       </c>
       <c r="H928" s="8">
         <f t="shared" si="183"/>
-        <v>1532890</v>
+        <v>4374290</v>
       </c>
       <c r="I928" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>160</v>
       </c>
       <c r="L928" s="2">
-        <f t="shared" si="184"/>
-        <v>1532890</v>
+        <f t="shared" si="185"/>
+        <v>4374290</v>
       </c>
       <c r="M928" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1276</v>
       </c>
       <c r="N928" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22214.947458995168</v>
       </c>
       <c r="O928" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36857.609862804886</v>
       </c>
       <c r="P928" s="16">
         <f>SUM($H$3:H928)</f>
-        <v>361811400</v>
+        <v>410098200</v>
       </c>
       <c r="Q928" s="2">
         <f>SUM($I$3:I928)</f>
-        <v>13424</v>
+        <v>15314</v>
       </c>
     </row>
     <row r="929" spans="1:17" x14ac:dyDescent="0.3">
@@ -56846,7 +56873,7 @@
         <v>1</v>
       </c>
       <c r="F929" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G929" s="17">
@@ -56855,34 +56882,35 @@
       </c>
       <c r="H929" s="8">
         <f t="shared" si="183"/>
-        <v>1544960</v>
+        <v>4467360</v>
       </c>
       <c r="I929" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>165</v>
       </c>
       <c r="L929" s="2">
-        <f t="shared" si="184"/>
-        <v>1544960</v>
+        <f t="shared" si="185"/>
+        <v>4467360</v>
       </c>
       <c r="M929" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1277</v>
       </c>
       <c r="N929" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22256.388479166788</v>
       </c>
       <c r="O929" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>36932.235372997835</v>
       </c>
       <c r="P929" s="16">
         <f>SUM($H$3:H929)</f>
-        <v>363356360</v>
+        <v>414565560</v>
       </c>
       <c r="Q929" s="2">
         <f>SUM($I$3:I929)</f>
-        <v>13449</v>
+        <v>15479</v>
       </c>
     </row>
     <row r="930" spans="1:17" x14ac:dyDescent="0.3">
@@ -56906,7 +56934,7 @@
         <v>1</v>
       </c>
       <c r="F930" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G930" s="17">
@@ -56915,34 +56943,35 @@
       </c>
       <c r="H930" s="8">
         <f t="shared" si="183"/>
-        <v>1557030</v>
+        <v>4560430</v>
       </c>
       <c r="I930" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>170</v>
       </c>
       <c r="L930" s="2">
-        <f t="shared" si="184"/>
-        <v>1557030</v>
+        <f t="shared" si="185"/>
+        <v>4560430</v>
       </c>
       <c r="M930" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1278</v>
       </c>
       <c r="N930" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22297.842720278124</v>
       </c>
       <c r="O930" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37006.908506377025</v>
       </c>
       <c r="P930" s="16">
         <f>SUM($H$3:H930)</f>
-        <v>364913390</v>
+        <v>419125990</v>
       </c>
       <c r="Q930" s="2">
         <f>SUM($I$3:I930)</f>
-        <v>13474</v>
+        <v>15649</v>
       </c>
     </row>
     <row r="931" spans="1:17" x14ac:dyDescent="0.3">
@@ -56966,7 +56995,7 @@
         <v>1</v>
       </c>
       <c r="F931" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G931" s="17">
@@ -56975,34 +57004,35 @@
       </c>
       <c r="H931" s="8">
         <f t="shared" si="183"/>
-        <v>1569100</v>
+        <v>4653500</v>
       </c>
       <c r="I931" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>175</v>
       </c>
       <c r="L931" s="2">
-        <f t="shared" si="184"/>
-        <v>1569100</v>
+        <f t="shared" si="185"/>
+        <v>4653500</v>
       </c>
       <c r="M931" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1279</v>
       </c>
       <c r="N931" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22339.310165484578</v>
       </c>
       <c r="O931" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37081.629217428243</v>
       </c>
       <c r="P931" s="16">
         <f>SUM($H$3:H931)</f>
-        <v>366482490</v>
+        <v>423779490</v>
       </c>
       <c r="Q931" s="2">
         <f>SUM($I$3:I931)</f>
-        <v>13499</v>
+        <v>15824</v>
       </c>
     </row>
     <row r="932" spans="1:17" x14ac:dyDescent="0.3">
@@ -57026,7 +57056,7 @@
         <v>1</v>
       </c>
       <c r="F932" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G932" s="17">
@@ -57035,34 +57065,35 @@
       </c>
       <c r="H932" s="8">
         <f t="shared" si="183"/>
-        <v>1581170</v>
+        <v>4746570</v>
       </c>
       <c r="I932" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>180</v>
       </c>
       <c r="L932" s="2">
-        <f t="shared" si="184"/>
-        <v>1581170</v>
+        <f t="shared" si="185"/>
+        <v>4746570</v>
       </c>
       <c r="M932" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1280</v>
       </c>
       <c r="N932" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22380.790797989655</v>
       </c>
       <c r="O932" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37156.397460752778</v>
       </c>
       <c r="P932" s="16">
         <f>SUM($H$3:H932)</f>
-        <v>368063660</v>
+        <v>428526060</v>
       </c>
       <c r="Q932" s="2">
         <f>SUM($I$3:I932)</f>
-        <v>13524</v>
+        <v>16004</v>
       </c>
     </row>
     <row r="933" spans="1:17" x14ac:dyDescent="0.3">
@@ -57086,7 +57117,7 @@
         <v>1</v>
       </c>
       <c r="F933" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G933" s="17">
@@ -57095,34 +57126,35 @@
       </c>
       <c r="H933" s="8">
         <f t="shared" si="183"/>
-        <v>1593240</v>
+        <v>4839640</v>
       </c>
       <c r="I933" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>185</v>
       </c>
       <c r="L933" s="2">
-        <f t="shared" si="184"/>
-        <v>1593240</v>
+        <f t="shared" si="185"/>
+        <v>4839640</v>
       </c>
       <c r="M933" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1281</v>
       </c>
       <c r="N933" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22422.284601044932</v>
       </c>
       <c r="O933" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37231.213191067429</v>
       </c>
       <c r="P933" s="16">
         <f>SUM($H$3:H933)</f>
-        <v>369656900</v>
+        <v>433365700</v>
       </c>
       <c r="Q933" s="2">
         <f>SUM($I$3:I933)</f>
-        <v>13549</v>
+        <v>16189</v>
       </c>
     </row>
     <row r="934" spans="1:17" x14ac:dyDescent="0.3">
@@ -57146,7 +57178,7 @@
         <v>1</v>
       </c>
       <c r="F934" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G934" s="17">
@@ -57155,34 +57187,35 @@
       </c>
       <c r="H934" s="8">
         <f t="shared" si="183"/>
-        <v>1605310</v>
+        <v>4932710</v>
       </c>
       <c r="I934" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>190</v>
       </c>
       <c r="L934" s="2">
-        <f t="shared" si="184"/>
-        <v>1605310</v>
+        <f t="shared" si="185"/>
+        <v>4932710</v>
       </c>
       <c r="M934" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1282</v>
       </c>
       <c r="N934" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22463.791557949742</v>
       </c>
       <c r="O934" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37306.07636320388</v>
       </c>
       <c r="P934" s="16">
         <f>SUM($H$3:H934)</f>
-        <v>371262210</v>
+        <v>438298410</v>
       </c>
       <c r="Q934" s="2">
         <f>SUM($I$3:I934)</f>
-        <v>13574</v>
+        <v>16379</v>
       </c>
     </row>
     <row r="935" spans="1:17" x14ac:dyDescent="0.3">
@@ -57206,43 +57239,44 @@
         <v>1</v>
       </c>
       <c r="F935" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G935" s="17">
-        <f t="shared" ref="G935:G998" si="189">0.01 + (A935-100)*(0.4-0.01)/(1000-100)</f>
+        <f t="shared" ref="G935:G998" si="190">0.01 + (A935-100)*(0.4-0.01)/(1000-100)</f>
         <v>0.37096666666666667</v>
       </c>
       <c r="H935" s="8">
         <f t="shared" si="183"/>
-        <v>1617380</v>
+        <v>5025780</v>
       </c>
       <c r="I935" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>195</v>
       </c>
       <c r="L935" s="2">
-        <f t="shared" si="184"/>
-        <v>1617380</v>
+        <f t="shared" si="185"/>
+        <v>5025780</v>
       </c>
       <c r="M935" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1283</v>
       </c>
       <c r="N935" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22505.311652050968</v>
       </c>
       <c r="O935" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37380.986932107968</v>
       </c>
       <c r="P935" s="16">
         <f>SUM($H$3:H935)</f>
-        <v>372879590</v>
+        <v>443324190</v>
       </c>
       <c r="Q935" s="2">
         <f>SUM($I$3:I935)</f>
-        <v>13599</v>
+        <v>16574</v>
       </c>
     </row>
     <row r="936" spans="1:17" x14ac:dyDescent="0.3">
@@ -57266,43 +57300,44 @@
         <v>1</v>
       </c>
       <c r="F936" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G936" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37140000000000001</v>
       </c>
       <c r="H936" s="8">
         <f t="shared" si="183"/>
-        <v>1629450</v>
+        <v>5118850</v>
       </c>
       <c r="I936" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>200</v>
       </c>
       <c r="L936" s="2">
-        <f t="shared" si="184"/>
-        <v>1629450</v>
+        <f t="shared" si="185"/>
+        <v>5118850</v>
       </c>
       <c r="M936" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1284</v>
       </c>
       <c r="N936" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22546.84486674294</v>
       </c>
       <c r="O936" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37455.944852839755</v>
       </c>
       <c r="P936" s="16">
         <f>SUM($H$3:H936)</f>
-        <v>374509040</v>
+        <v>448443040</v>
       </c>
       <c r="Q936" s="2">
         <f>SUM($I$3:I936)</f>
-        <v>13624</v>
+        <v>16774</v>
       </c>
     </row>
     <row r="937" spans="1:17" x14ac:dyDescent="0.3">
@@ -57326,43 +57361,44 @@
         <v>1</v>
       </c>
       <c r="F937" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G937" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.3718333333333334</v>
       </c>
       <c r="H937" s="8">
         <f t="shared" si="183"/>
-        <v>1641520</v>
+        <v>5211920</v>
       </c>
       <c r="I937" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>205</v>
       </c>
       <c r="L937" s="2">
-        <f t="shared" si="184"/>
-        <v>1641520</v>
+        <f t="shared" si="185"/>
+        <v>5211920</v>
       </c>
       <c r="M937" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1285</v>
       </c>
       <c r="N937" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22588.391185467037</v>
       </c>
       <c r="O937" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37530.950080572547</v>
       </c>
       <c r="P937" s="16">
         <f>SUM($H$3:H937)</f>
-        <v>376150560</v>
+        <v>453654960</v>
       </c>
       <c r="Q937" s="2">
         <f>SUM($I$3:I937)</f>
-        <v>13649</v>
+        <v>16979</v>
       </c>
     </row>
     <row r="938" spans="1:17" x14ac:dyDescent="0.3">
@@ -57386,43 +57422,44 @@
         <v>1</v>
       </c>
       <c r="F938" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G938" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37226666666666669</v>
       </c>
       <c r="H938" s="8">
         <f t="shared" si="183"/>
-        <v>1653590</v>
+        <v>5304990</v>
       </c>
       <c r="I938" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>210</v>
       </c>
       <c r="L938" s="2">
-        <f t="shared" si="184"/>
-        <v>1653590</v>
+        <f t="shared" si="185"/>
+        <v>5304990</v>
       </c>
       <c r="M938" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1286</v>
       </c>
       <c r="N938" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22629.950591711626</v>
       </c>
       <c r="O938" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37606.002570592726</v>
       </c>
       <c r="P938" s="16">
         <f>SUM($H$3:H938)</f>
-        <v>377804150</v>
+        <v>458959950</v>
       </c>
       <c r="Q938" s="2">
         <f>SUM($I$3:I938)</f>
-        <v>13674</v>
+        <v>17189</v>
       </c>
     </row>
     <row r="939" spans="1:17" x14ac:dyDescent="0.3">
@@ -57446,43 +57483,44 @@
         <v>1</v>
       </c>
       <c r="F939" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G939" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37270000000000003</v>
       </c>
       <c r="H939" s="8">
         <f t="shared" si="183"/>
-        <v>1665660</v>
+        <v>5398060</v>
       </c>
       <c r="I939" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>215</v>
       </c>
       <c r="L939" s="2">
-        <f t="shared" si="184"/>
-        <v>1665660</v>
+        <f t="shared" si="185"/>
+        <v>5398060</v>
       </c>
       <c r="M939" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1287</v>
       </c>
       <c r="N939" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22671.523069011837</v>
       </c>
       <c r="O939" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37681.102278299186</v>
       </c>
       <c r="P939" s="16">
         <f>SUM($H$3:H939)</f>
-        <v>379469810</v>
+        <v>464358010</v>
       </c>
       <c r="Q939" s="2">
         <f>SUM($I$3:I939)</f>
-        <v>13699</v>
+        <v>17404</v>
       </c>
     </row>
     <row r="940" spans="1:17" x14ac:dyDescent="0.3">
@@ -57506,43 +57544,44 @@
         <v>1</v>
       </c>
       <c r="F940" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G940" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37313333333333332</v>
       </c>
       <c r="H940" s="8">
         <f t="shared" si="183"/>
-        <v>1677730</v>
+        <v>5491130</v>
       </c>
       <c r="I940" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>220</v>
       </c>
       <c r="L940" s="2">
-        <f t="shared" si="184"/>
-        <v>1677730</v>
+        <f t="shared" si="185"/>
+        <v>5491130</v>
       </c>
       <c r="M940" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1288</v>
       </c>
       <c r="N940" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22713.10860094929</v>
       </c>
       <c r="O940" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37756.249159202758</v>
       </c>
       <c r="P940" s="16">
         <f>SUM($H$3:H940)</f>
-        <v>381147540</v>
+        <v>469849140</v>
       </c>
       <c r="Q940" s="2">
         <f>SUM($I$3:I940)</f>
-        <v>13724</v>
+        <v>17624</v>
       </c>
     </row>
     <row r="941" spans="1:17" x14ac:dyDescent="0.3">
@@ -57566,43 +57605,44 @@
         <v>1</v>
       </c>
       <c r="F941" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.6000000000000014</v>
       </c>
       <c r="G941" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37356666666666671</v>
       </c>
       <c r="H941" s="8">
         <f t="shared" si="183"/>
-        <v>1689800</v>
+        <v>5584200</v>
       </c>
       <c r="I941" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>225</v>
       </c>
       <c r="L941" s="2">
-        <f t="shared" si="184"/>
-        <v>1689800</v>
+        <f t="shared" si="185"/>
+        <v>5584200</v>
       </c>
       <c r="M941" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1289</v>
       </c>
       <c r="N941" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22754.70717115196</v>
       </c>
       <c r="O941" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37831.443168926104</v>
       </c>
       <c r="P941" s="16">
         <f>SUM($H$3:H941)</f>
-        <v>382837340</v>
+        <v>475433340</v>
       </c>
       <c r="Q941" s="2">
         <f>SUM($I$3:I941)</f>
-        <v>13749</v>
+        <v>17849</v>
       </c>
     </row>
     <row r="942" spans="1:17" x14ac:dyDescent="0.3">
@@ -57626,43 +57666,44 @@
         <v>1</v>
       </c>
       <c r="F942" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G942" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37400000000000005</v>
       </c>
       <c r="H942" s="8">
         <f t="shared" si="183"/>
-        <v>1701870</v>
+        <v>5677270</v>
       </c>
       <c r="I942" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>230</v>
       </c>
       <c r="L942" s="2">
-        <f t="shared" si="184"/>
-        <v>1701870</v>
+        <f t="shared" si="185"/>
+        <v>5677270</v>
       </c>
       <c r="M942" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1290</v>
       </c>
       <c r="N942" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22796.31876329397</v>
       </c>
       <c r="O942" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37906.684263202922</v>
       </c>
       <c r="P942" s="16">
         <f>SUM($H$3:H942)</f>
-        <v>384539210</v>
+        <v>481110610</v>
       </c>
       <c r="Q942" s="2">
         <f>SUM($I$3:I942)</f>
-        <v>13774</v>
+        <v>18079</v>
       </c>
     </row>
     <row r="943" spans="1:17" x14ac:dyDescent="0.3">
@@ -57686,43 +57727,44 @@
         <v>1</v>
       </c>
       <c r="F943" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G943" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37443333333333334</v>
       </c>
       <c r="H943" s="8">
         <f t="shared" si="183"/>
-        <v>1713940</v>
+        <v>5770340</v>
       </c>
       <c r="I943" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>235</v>
       </c>
       <c r="L943" s="2">
-        <f t="shared" si="184"/>
-        <v>1713940</v>
+        <f t="shared" si="185"/>
+        <v>5770340</v>
       </c>
       <c r="M943" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1291</v>
       </c>
       <c r="N943" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22837.943361095287</v>
       </c>
       <c r="O943" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>37981.972397877536</v>
       </c>
       <c r="P943" s="16">
         <f>SUM($H$3:H943)</f>
-        <v>386253150</v>
+        <v>486880950</v>
       </c>
       <c r="Q943" s="2">
         <f>SUM($I$3:I943)</f>
-        <v>13799</v>
+        <v>18314</v>
       </c>
     </row>
     <row r="944" spans="1:17" x14ac:dyDescent="0.3">
@@ -57735,54 +57777,55 @@
         <v>1292</v>
       </c>
       <c r="C944" s="14">
-        <f t="shared" ref="C944:C1001" si="190">9.525*(A944-300)^1.2 + 600</f>
+        <f t="shared" ref="C944:C1001" si="191">9.525*(A944-300)^1.2 + 600</f>
         <v>22879.580948321694</v>
       </c>
       <c r="D944" s="14">
-        <f t="shared" ref="D944:D1001" si="191">4.055*(A944-300)^1.4 + 3500</f>
+        <f t="shared" ref="D944:D1001" si="192">4.055*(A944-300)^1.4 + 3500</f>
         <v>38057.307528904574</v>
       </c>
       <c r="E944" s="2">
         <v>1</v>
       </c>
       <c r="F944" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G944" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37486666666666668</v>
       </c>
       <c r="H944" s="8">
         <f t="shared" si="183"/>
-        <v>1726010</v>
+        <v>5863410</v>
       </c>
       <c r="I944" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>240</v>
       </c>
       <c r="L944" s="2">
-        <f t="shared" si="184"/>
-        <v>1726010</v>
+        <f t="shared" si="185"/>
+        <v>5863410</v>
       </c>
       <c r="M944" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1292</v>
       </c>
       <c r="N944" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22879.580948321694</v>
       </c>
       <c r="O944" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38057.307528904574</v>
       </c>
       <c r="P944" s="16">
         <f>SUM($H$3:H944)</f>
-        <v>387979160</v>
+        <v>492744360</v>
       </c>
       <c r="Q944" s="2">
         <f>SUM($I$3:I944)</f>
-        <v>13824</v>
+        <v>18554</v>
       </c>
     </row>
     <row r="945" spans="1:17" x14ac:dyDescent="0.3">
@@ -57795,54 +57838,55 @@
         <v>1293</v>
       </c>
       <c r="C945" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>22921.231508784454</v>
       </c>
       <c r="D945" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38132.689612348622</v>
       </c>
       <c r="E945" s="2">
         <v>1</v>
       </c>
       <c r="F945" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G945" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37530000000000008</v>
       </c>
       <c r="H945" s="8">
         <f t="shared" si="183"/>
-        <v>1738080</v>
+        <v>5956480</v>
       </c>
       <c r="I945" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>245</v>
       </c>
       <c r="L945" s="2">
-        <f t="shared" si="184"/>
-        <v>1738080</v>
+        <f t="shared" si="185"/>
+        <v>5956480</v>
       </c>
       <c r="M945" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1293</v>
       </c>
       <c r="N945" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22921.231508784454</v>
       </c>
       <c r="O945" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38132.689612348622</v>
       </c>
       <c r="P945" s="16">
         <f>SUM($H$3:H945)</f>
-        <v>389717240</v>
+        <v>498700840</v>
       </c>
       <c r="Q945" s="2">
         <f>SUM($I$3:I945)</f>
-        <v>13849</v>
+        <v>18799</v>
       </c>
     </row>
     <row r="946" spans="1:17" x14ac:dyDescent="0.3">
@@ -57855,54 +57899,55 @@
         <v>1294</v>
       </c>
       <c r="C946" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>22962.89502634016</v>
       </c>
       <c r="D946" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38208.118604383417</v>
       </c>
       <c r="E946" s="2">
         <v>1</v>
       </c>
       <c r="F946" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G946" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37573333333333336</v>
       </c>
       <c r="H946" s="8">
         <f t="shared" si="183"/>
-        <v>1750150</v>
+        <v>6049550</v>
       </c>
       <c r="I946" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>250</v>
       </c>
       <c r="L946" s="2">
-        <f t="shared" si="184"/>
-        <v>1750150</v>
+        <f t="shared" si="185"/>
+        <v>6049550</v>
       </c>
       <c r="M946" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1294</v>
       </c>
       <c r="N946" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>22962.89502634016</v>
       </c>
       <c r="O946" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38208.118604383417</v>
       </c>
       <c r="P946" s="16">
         <f>SUM($H$3:H946)</f>
-        <v>391467390</v>
+        <v>504750390</v>
       </c>
       <c r="Q946" s="2">
         <f>SUM($I$3:I946)</f>
-        <v>13874</v>
+        <v>19049</v>
       </c>
     </row>
     <row r="947" spans="1:17" x14ac:dyDescent="0.3">
@@ -57915,54 +57960,55 @@
         <v>1295</v>
       </c>
       <c r="C947" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23004.571484890486</v>
       </c>
       <c r="D947" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38283.594461291628</v>
       </c>
       <c r="E947" s="2">
         <v>1</v>
       </c>
       <c r="F947" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G947" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.3761666666666667</v>
       </c>
       <c r="H947" s="8">
         <f t="shared" si="183"/>
-        <v>1762220</v>
+        <v>6142620</v>
       </c>
       <c r="I947" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>255</v>
       </c>
       <c r="L947" s="2">
-        <f t="shared" si="184"/>
-        <v>1762220</v>
+        <f t="shared" si="185"/>
+        <v>6142620</v>
       </c>
       <c r="M947" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1295</v>
       </c>
       <c r="N947" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23004.571484890486</v>
       </c>
       <c r="O947" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38283.594461291628</v>
       </c>
       <c r="P947" s="16">
         <f>SUM($H$3:H947)</f>
-        <v>393229610</v>
+        <v>510893010</v>
       </c>
       <c r="Q947" s="2">
         <f>SUM($I$3:I947)</f>
-        <v>13899</v>
+        <v>19304</v>
       </c>
     </row>
     <row r="948" spans="1:17" x14ac:dyDescent="0.3">
@@ -57975,54 +58021,55 @@
         <v>1296</v>
       </c>
       <c r="C948" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23046.260868382127</v>
       </c>
       <c r="D948" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38359.117139464564</v>
       </c>
       <c r="E948" s="2">
         <v>1</v>
       </c>
       <c r="F948" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G948" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37659999999999999</v>
       </c>
       <c r="H948" s="8">
         <f t="shared" si="183"/>
-        <v>1774290</v>
+        <v>6235690</v>
       </c>
       <c r="I948" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>260</v>
       </c>
       <c r="L948" s="2">
-        <f t="shared" si="184"/>
-        <v>1774290</v>
+        <f t="shared" si="185"/>
+        <v>6235690</v>
       </c>
       <c r="M948" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1296</v>
       </c>
       <c r="N948" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23046.260868382127</v>
       </c>
       <c r="O948" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38359.117139464564</v>
       </c>
       <c r="P948" s="16">
         <f>SUM($H$3:H948)</f>
-        <v>395003900</v>
+        <v>517128700</v>
       </c>
       <c r="Q948" s="2">
         <f>SUM($I$3:I948)</f>
-        <v>13924</v>
+        <v>19564</v>
       </c>
     </row>
     <row r="949" spans="1:17" x14ac:dyDescent="0.3">
@@ -58035,54 +58082,55 @@
         <v>1297</v>
       </c>
       <c r="C949" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23087.963160806492</v>
       </c>
       <c r="D949" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38434.686595401494</v>
       </c>
       <c r="E949" s="2">
         <v>1</v>
       </c>
       <c r="F949" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G949" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37703333333333333</v>
       </c>
       <c r="H949" s="8">
         <f t="shared" si="183"/>
-        <v>1786360</v>
+        <v>6328760</v>
       </c>
       <c r="I949" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>265</v>
       </c>
       <c r="L949" s="2">
-        <f t="shared" si="184"/>
-        <v>1786360</v>
+        <f t="shared" si="185"/>
+        <v>6328760</v>
       </c>
       <c r="M949" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1297</v>
       </c>
       <c r="N949" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23087.963160806492</v>
       </c>
       <c r="O949" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38434.686595401494</v>
       </c>
       <c r="P949" s="16">
         <f>SUM($H$3:H949)</f>
-        <v>396790260</v>
+        <v>523457460</v>
       </c>
       <c r="Q949" s="2">
         <f>SUM($I$3:I949)</f>
-        <v>13949</v>
+        <v>19829</v>
       </c>
     </row>
     <row r="950" spans="1:17" x14ac:dyDescent="0.3">
@@ -58095,54 +58143,55 @@
         <v>1298</v>
       </c>
       <c r="C950" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23129.678346199456</v>
       </c>
       <c r="D950" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38510.302785709144</v>
       </c>
       <c r="E950" s="2">
         <v>1</v>
       </c>
       <c r="F950" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G950" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37746666666666673</v>
       </c>
       <c r="H950" s="8">
         <f t="shared" si="183"/>
-        <v>1798430</v>
+        <v>6421830</v>
       </c>
       <c r="I950" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>270</v>
       </c>
       <c r="L950" s="2">
-        <f t="shared" si="184"/>
-        <v>1798430</v>
+        <f t="shared" si="185"/>
+        <v>6421830</v>
       </c>
       <c r="M950" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1298</v>
       </c>
       <c r="N950" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23129.678346199456</v>
       </c>
       <c r="O950" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38510.302785709144</v>
       </c>
       <c r="P950" s="16">
         <f>SUM($H$3:H950)</f>
-        <v>398588690</v>
+        <v>529879290</v>
       </c>
       <c r="Q950" s="2">
         <f>SUM($I$3:I950)</f>
-        <v>13974</v>
+        <v>20099</v>
       </c>
     </row>
     <row r="951" spans="1:17" x14ac:dyDescent="0.3">
@@ -58155,54 +58204,55 @@
         <v>1299</v>
       </c>
       <c r="C951" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23171.406408641371</v>
       </c>
       <c r="D951" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38585.965667101707</v>
       </c>
       <c r="E951" s="2">
         <v>1</v>
       </c>
       <c r="F951" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G951" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37790000000000001</v>
       </c>
       <c r="H951" s="8">
         <f t="shared" si="183"/>
-        <v>1810500</v>
+        <v>6514900</v>
       </c>
       <c r="I951" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>275</v>
       </c>
       <c r="L951" s="2">
-        <f t="shared" si="184"/>
-        <v>1810500</v>
+        <f t="shared" si="185"/>
+        <v>6514900</v>
       </c>
       <c r="M951" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1299</v>
       </c>
       <c r="N951" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23171.406408641371</v>
       </c>
       <c r="O951" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38585.965667101707</v>
       </c>
       <c r="P951" s="16">
         <f>SUM($H$3:H951)</f>
-        <v>400399190</v>
+        <v>536394190</v>
       </c>
       <c r="Q951" s="2">
         <f>SUM($I$3:I951)</f>
-        <v>13999</v>
+        <v>20374</v>
       </c>
     </row>
     <row r="952" spans="1:17" x14ac:dyDescent="0.3">
@@ -58215,54 +58265,55 @@
         <v>1300</v>
       </c>
       <c r="C952" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23213.147332256602</v>
       </c>
       <c r="D952" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38661.675196399869</v>
       </c>
       <c r="E952" s="2">
         <v>1</v>
       </c>
       <c r="F952" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G952" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37833333333333335</v>
       </c>
       <c r="H952" s="8">
         <f t="shared" si="183"/>
-        <v>1822570</v>
+        <v>6607970</v>
       </c>
       <c r="I952" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>280</v>
       </c>
       <c r="L952" s="2">
-        <f t="shared" si="184"/>
-        <v>1822570</v>
+        <f t="shared" si="185"/>
+        <v>6607970</v>
       </c>
       <c r="M952" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1300</v>
       </c>
       <c r="N952" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23213.147332256602</v>
       </c>
       <c r="O952" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38661.675196399869</v>
       </c>
       <c r="P952" s="16">
         <f>SUM($H$3:H952)</f>
-        <v>402221760</v>
+        <v>543002160</v>
       </c>
       <c r="Q952" s="2">
         <f>SUM($I$3:I952)</f>
-        <v>14024</v>
+        <v>20654</v>
       </c>
     </row>
     <row r="953" spans="1:17" x14ac:dyDescent="0.3">
@@ -58275,54 +58326,55 @@
         <v>1301</v>
       </c>
       <c r="C953" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23254.901101213629</v>
       </c>
       <c r="D953" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38737.431330530839</v>
       </c>
       <c r="E953" s="2">
         <v>1</v>
       </c>
       <c r="F953" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G953" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37876666666666664</v>
       </c>
       <c r="H953" s="8">
         <f t="shared" si="183"/>
-        <v>1834640</v>
+        <v>6701040</v>
       </c>
       <c r="I953" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>285</v>
       </c>
       <c r="L953" s="2">
-        <f t="shared" si="184"/>
-        <v>1834640</v>
+        <f t="shared" si="185"/>
+        <v>6701040</v>
       </c>
       <c r="M953" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1301</v>
       </c>
       <c r="N953" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23254.901101213629</v>
       </c>
       <c r="O953" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38737.431330530839</v>
       </c>
       <c r="P953" s="16">
         <f>SUM($H$3:H953)</f>
-        <v>404056400</v>
+        <v>549703200</v>
       </c>
       <c r="Q953" s="2">
         <f>SUM($I$3:I953)</f>
-        <v>14049</v>
+        <v>20939</v>
       </c>
     </row>
     <row r="954" spans="1:17" x14ac:dyDescent="0.3">
@@ -58335,54 +58387,55 @@
         <v>1302</v>
       </c>
       <c r="C954" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23296.667699724665</v>
       </c>
       <c r="D954" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38813.234026527556</v>
       </c>
       <c r="E954" s="2">
         <v>1</v>
       </c>
       <c r="F954" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G954" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37920000000000004</v>
       </c>
       <c r="H954" s="8">
         <f t="shared" si="183"/>
-        <v>1846710</v>
+        <v>6794110</v>
       </c>
       <c r="I954" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>290</v>
       </c>
       <c r="L954" s="2">
-        <f t="shared" si="184"/>
-        <v>1846710</v>
+        <f t="shared" si="185"/>
+        <v>6794110</v>
       </c>
       <c r="M954" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1302</v>
       </c>
       <c r="N954" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23296.667699724665</v>
       </c>
       <c r="O954" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38813.234026527556</v>
       </c>
       <c r="P954" s="16">
         <f>SUM($H$3:H954)</f>
-        <v>405903110</v>
+        <v>556497310</v>
       </c>
       <c r="Q954" s="2">
         <f>SUM($I$3:I954)</f>
-        <v>14074</v>
+        <v>21229</v>
       </c>
     </row>
     <row r="955" spans="1:17" x14ac:dyDescent="0.3">
@@ -58395,54 +58448,55 @@
         <v>1303</v>
       </c>
       <c r="C955" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23338.447112045433</v>
       </c>
       <c r="D955" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38889.083241528519</v>
       </c>
       <c r="E955" s="2">
         <v>1</v>
       </c>
       <c r="F955" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G955" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.37963333333333338</v>
       </c>
       <c r="H955" s="8">
         <f t="shared" si="183"/>
-        <v>1858780</v>
+        <v>6887180</v>
       </c>
       <c r="I955" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>295</v>
       </c>
       <c r="L955" s="2">
-        <f t="shared" si="184"/>
-        <v>1858780</v>
+        <f t="shared" si="185"/>
+        <v>6887180</v>
       </c>
       <c r="M955" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1303</v>
       </c>
       <c r="N955" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23338.447112045433</v>
       </c>
       <c r="O955" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38889.083241528519</v>
       </c>
       <c r="P955" s="16">
         <f>SUM($H$3:H955)</f>
-        <v>407761890</v>
+        <v>563384490</v>
       </c>
       <c r="Q955" s="2">
         <f>SUM($I$3:I955)</f>
-        <v>14099</v>
+        <v>21524</v>
       </c>
     </row>
     <row r="956" spans="1:17" x14ac:dyDescent="0.3">
@@ -58455,54 +58509,55 @@
         <v>1304</v>
       </c>
       <c r="C956" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23380.239322475169</v>
       </c>
       <c r="D956" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>38964.978932777216</v>
       </c>
       <c r="E956" s="2">
         <v>1</v>
       </c>
       <c r="F956" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G956" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38006666666666666</v>
       </c>
       <c r="H956" s="8">
         <f t="shared" si="183"/>
-        <v>1870850</v>
+        <v>6980250</v>
       </c>
       <c r="I956" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>300</v>
       </c>
       <c r="L956" s="2">
-        <f t="shared" si="184"/>
-        <v>1870850</v>
+        <f t="shared" si="185"/>
+        <v>6980250</v>
       </c>
       <c r="M956" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1304</v>
       </c>
       <c r="N956" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23380.239322475169</v>
       </c>
       <c r="O956" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>38964.978932777216</v>
       </c>
       <c r="P956" s="16">
         <f>SUM($H$3:H956)</f>
-        <v>409632740</v>
+        <v>570364740</v>
       </c>
       <c r="Q956" s="2">
         <f>SUM($I$3:I956)</f>
-        <v>14124</v>
+        <v>21824</v>
       </c>
     </row>
     <row r="957" spans="1:17" x14ac:dyDescent="0.3">
@@ -58515,54 +58570,55 @@
         <v>1305</v>
       </c>
       <c r="C957" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23422.044315356259</v>
       </c>
       <c r="D957" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39040.92105762189</v>
       </c>
       <c r="E957" s="2">
         <v>1</v>
       </c>
       <c r="F957" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G957" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.3805</v>
       </c>
       <c r="H957" s="8">
         <f t="shared" si="183"/>
-        <v>1882920</v>
+        <v>7073320</v>
       </c>
       <c r="I957" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>305</v>
       </c>
       <c r="L957" s="2">
-        <f t="shared" si="184"/>
-        <v>1882920</v>
+        <f t="shared" si="185"/>
+        <v>7073320</v>
       </c>
       <c r="M957" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1305</v>
       </c>
       <c r="N957" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23422.044315356259</v>
       </c>
       <c r="O957" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39040.92105762189</v>
       </c>
       <c r="P957" s="16">
         <f>SUM($H$3:H957)</f>
-        <v>411515660</v>
+        <v>577438060</v>
       </c>
       <c r="Q957" s="2">
         <f>SUM($I$3:I957)</f>
-        <v>14149</v>
+        <v>22129</v>
       </c>
     </row>
     <row r="958" spans="1:17" x14ac:dyDescent="0.3">
@@ -58575,54 +58631,55 @@
         <v>1306</v>
       </c>
       <c r="C958" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23463.86207507419</v>
       </c>
       <c r="D958" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39116.909573514829</v>
       </c>
       <c r="E958" s="2">
         <v>1</v>
       </c>
       <c r="F958" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G958" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.3809333333333334</v>
       </c>
       <c r="H958" s="8">
         <f t="shared" si="183"/>
-        <v>1894990</v>
+        <v>7166390</v>
       </c>
       <c r="I958" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>310</v>
       </c>
       <c r="L958" s="2">
-        <f t="shared" si="184"/>
-        <v>1894990</v>
+        <f t="shared" si="185"/>
+        <v>7166390</v>
       </c>
       <c r="M958" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1306</v>
       </c>
       <c r="N958" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23463.86207507419</v>
       </c>
       <c r="O958" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39116.909573514829</v>
       </c>
       <c r="P958" s="16">
         <f>SUM($H$3:H958)</f>
-        <v>413410650</v>
+        <v>584604450</v>
       </c>
       <c r="Q958" s="2">
         <f>SUM($I$3:I958)</f>
-        <v>14174</v>
+        <v>22439</v>
       </c>
     </row>
     <row r="959" spans="1:17" x14ac:dyDescent="0.3">
@@ -58635,54 +58692,55 @@
         <v>1307</v>
       </c>
       <c r="C959" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23505.692586057223</v>
       </c>
       <c r="D959" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39192.944438012288</v>
       </c>
       <c r="E959" s="2">
         <v>1</v>
       </c>
       <c r="F959" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G959" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38136666666666669</v>
       </c>
       <c r="H959" s="8">
         <f t="shared" si="183"/>
-        <v>1907060</v>
+        <v>7259460</v>
       </c>
       <c r="I959" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>315</v>
       </c>
       <c r="L959" s="2">
-        <f t="shared" si="184"/>
-        <v>1907060</v>
+        <f t="shared" si="185"/>
+        <v>7259460</v>
       </c>
       <c r="M959" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1307</v>
       </c>
       <c r="N959" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23505.692586057223</v>
       </c>
       <c r="O959" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39192.944438012288</v>
       </c>
       <c r="P959" s="16">
         <f>SUM($H$3:H959)</f>
-        <v>415317710</v>
+        <v>591863910</v>
       </c>
       <c r="Q959" s="2">
         <f>SUM($I$3:I959)</f>
-        <v>14199</v>
+        <v>22754</v>
       </c>
     </row>
     <row r="960" spans="1:17" x14ac:dyDescent="0.3">
@@ -58695,54 +58753,55 @@
         <v>1308</v>
       </c>
       <c r="C960" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23547.53583277639</v>
       </c>
       <c r="D960" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39269.025608773838</v>
       </c>
       <c r="E960" s="2">
         <v>1</v>
       </c>
       <c r="F960" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G960" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38180000000000003</v>
       </c>
       <c r="H960" s="8">
         <f t="shared" si="183"/>
-        <v>1919130</v>
+        <v>7352530</v>
       </c>
       <c r="I960" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>320</v>
       </c>
       <c r="L960" s="2">
-        <f t="shared" si="184"/>
-        <v>1919130</v>
+        <f t="shared" si="185"/>
+        <v>7352530</v>
       </c>
       <c r="M960" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1308</v>
       </c>
       <c r="N960" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23547.53583277639</v>
       </c>
       <c r="O960" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39269.025608773838</v>
       </c>
       <c r="P960" s="16">
         <f>SUM($H$3:H960)</f>
-        <v>417236840</v>
+        <v>599216440</v>
       </c>
       <c r="Q960" s="2">
         <f>SUM($I$3:I960)</f>
-        <v>14224</v>
+        <v>23074</v>
       </c>
     </row>
     <row r="961" spans="1:17" x14ac:dyDescent="0.3">
@@ -58755,54 +58814,55 @@
         <v>1309</v>
       </c>
       <c r="C961" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23589.391799745081</v>
       </c>
       <c r="D961" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39345.153043562095</v>
       </c>
       <c r="E961" s="2">
         <v>1</v>
       </c>
       <c r="F961" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="G961" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38223333333333331</v>
       </c>
       <c r="H961" s="8">
         <f t="shared" si="183"/>
-        <v>1931200</v>
+        <v>7445600</v>
       </c>
       <c r="I961" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>325</v>
       </c>
       <c r="L961" s="2">
-        <f t="shared" si="184"/>
-        <v>1931200</v>
+        <f t="shared" si="185"/>
+        <v>7445600</v>
       </c>
       <c r="M961" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1309</v>
       </c>
       <c r="N961" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23589.391799745081</v>
       </c>
       <c r="O961" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39345.153043562095</v>
       </c>
       <c r="P961" s="16">
         <f>SUM($H$3:H961)</f>
-        <v>419168040</v>
+        <v>606662040</v>
       </c>
       <c r="Q961" s="2">
         <f>SUM($I$3:I961)</f>
-        <v>14249</v>
+        <v>23399</v>
       </c>
     </row>
     <row r="962" spans="1:17" x14ac:dyDescent="0.3">
@@ -58815,54 +58875,55 @@
         <v>1310</v>
       </c>
       <c r="C962" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23631.260471519083</v>
       </c>
       <c r="D962" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39421.326700242098</v>
       </c>
       <c r="E962" s="2">
         <v>1</v>
       </c>
       <c r="F962" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>9</v>
       </c>
       <c r="G962" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38266666666666671</v>
       </c>
       <c r="H962" s="8">
         <f t="shared" si="183"/>
-        <v>1943270</v>
+        <v>7538670</v>
       </c>
       <c r="I962" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>330</v>
       </c>
       <c r="L962" s="2">
-        <f t="shared" si="184"/>
-        <v>1943270</v>
+        <f t="shared" si="185"/>
+        <v>7538670</v>
       </c>
       <c r="M962" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1310</v>
       </c>
       <c r="N962" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23631.260471519083</v>
       </c>
       <c r="O962" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39421.326700242098</v>
       </c>
       <c r="P962" s="16">
         <f>SUM($H$3:H962)</f>
-        <v>421111310</v>
+        <v>614200710</v>
       </c>
       <c r="Q962" s="2">
         <f>SUM($I$3:I962)</f>
-        <v>14274</v>
+        <v>23729</v>
       </c>
     </row>
     <row r="963" spans="1:17" x14ac:dyDescent="0.3">
@@ -58875,54 +58936,55 @@
         <v>1311</v>
       </c>
       <c r="C963" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23673.141832696288</v>
       </c>
       <c r="D963" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39497.546536781294</v>
       </c>
       <c r="E963" s="2">
         <v>1</v>
       </c>
       <c r="F963" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>9</v>
       </c>
       <c r="G963" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38310000000000005</v>
       </c>
       <c r="H963" s="8">
         <f t="shared" si="183"/>
-        <v>1955340</v>
+        <v>7631740</v>
       </c>
       <c r="I963" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>335</v>
       </c>
       <c r="L963" s="2">
-        <f t="shared" si="184"/>
-        <v>1955340</v>
+        <f t="shared" si="185"/>
+        <v>7631740</v>
       </c>
       <c r="M963" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1311</v>
       </c>
       <c r="N963" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23673.141832696288</v>
       </c>
       <c r="O963" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39497.546536781294</v>
       </c>
       <c r="P963" s="16">
         <f>SUM($H$3:H963)</f>
-        <v>423066650</v>
+        <v>621832450</v>
       </c>
       <c r="Q963" s="2">
         <f>SUM($I$3:I963)</f>
-        <v>14299</v>
+        <v>24064</v>
       </c>
     </row>
     <row r="964" spans="1:17" x14ac:dyDescent="0.3">
@@ -58935,2283 +58997,2321 @@
         <v>1312</v>
       </c>
       <c r="C964" s="14">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>23715.035867916551</v>
       </c>
       <c r="D964" s="14">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>39573.812511248783</v>
       </c>
       <c r="E964" s="2">
         <v>1</v>
       </c>
       <c r="F964" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>9</v>
       </c>
       <c r="G964" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38353333333333334</v>
       </c>
       <c r="H964" s="8">
         <f t="shared" si="183"/>
-        <v>1967410</v>
+        <v>7724810</v>
       </c>
       <c r="I964" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>340</v>
       </c>
       <c r="L964" s="2">
-        <f t="shared" si="184"/>
-        <v>1967410</v>
+        <f t="shared" si="185"/>
+        <v>7724810</v>
       </c>
       <c r="M964" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1312</v>
       </c>
       <c r="N964" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23715.035867916551</v>
       </c>
       <c r="O964" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39573.812511248783</v>
       </c>
       <c r="P964" s="16">
         <f>SUM($H$3:H964)</f>
-        <v>425034060</v>
+        <v>629557260</v>
       </c>
       <c r="Q964" s="2">
         <f>SUM($I$3:I964)</f>
-        <v>14324</v>
+        <v>24404</v>
       </c>
     </row>
     <row r="965" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A965" s="7">
-        <f t="shared" ref="A965:B1002" si="192">A964+1</f>
+        <f t="shared" ref="A965:B1002" si="193">A964+1</f>
         <v>963</v>
       </c>
       <c r="B965" s="2">
+        <f t="shared" si="193"/>
+        <v>1313</v>
+      </c>
+      <c r="C965" s="14">
+        <f t="shared" si="191"/>
+        <v>23756.942561861459</v>
+      </c>
+      <c r="D965" s="14">
         <f t="shared" si="192"/>
-        <v>1313</v>
-      </c>
-      <c r="C965" s="14">
-        <f t="shared" si="190"/>
-        <v>23756.942561861459</v>
-      </c>
-      <c r="D965" s="14">
-        <f t="shared" si="191"/>
         <v>39650.124581814969</v>
       </c>
       <c r="E965" s="2">
         <v>1</v>
       </c>
       <c r="F965" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>9</v>
       </c>
       <c r="G965" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38396666666666668</v>
       </c>
       <c r="H965" s="8">
         <f t="shared" si="183"/>
-        <v>1979480</v>
+        <v>7817880</v>
       </c>
       <c r="I965" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>345</v>
       </c>
       <c r="L965" s="2">
-        <f t="shared" si="184"/>
-        <v>1979480</v>
+        <f t="shared" si="185"/>
+        <v>7817880</v>
       </c>
       <c r="M965" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1313</v>
       </c>
       <c r="N965" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23756.942561861459</v>
       </c>
       <c r="O965" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39650.124581814969</v>
       </c>
       <c r="P965" s="16">
         <f>SUM($H$3:H965)</f>
-        <v>427013540</v>
+        <v>637375140</v>
       </c>
       <c r="Q965" s="2">
         <f>SUM($I$3:I965)</f>
-        <v>14349</v>
+        <v>24749</v>
       </c>
     </row>
     <row r="966" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A966" s="7">
+        <f t="shared" si="193"/>
+        <v>964</v>
+      </c>
+      <c r="B966" s="2">
+        <f t="shared" si="193"/>
+        <v>1314</v>
+      </c>
+      <c r="C966" s="14">
+        <f t="shared" si="191"/>
+        <v>23798.861899254214</v>
+      </c>
+      <c r="D966" s="14">
         <f t="shared" si="192"/>
-        <v>964</v>
-      </c>
-      <c r="B966" s="2">
-        <f t="shared" si="192"/>
-        <v>1314</v>
-      </c>
-      <c r="C966" s="14">
-        <f t="shared" si="190"/>
-        <v>23798.861899254214</v>
-      </c>
-      <c r="D966" s="14">
-        <f t="shared" si="191"/>
         <v>39726.482706751362</v>
       </c>
       <c r="E966" s="2">
         <v>1</v>
       </c>
       <c r="F966" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>9</v>
       </c>
       <c r="G966" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38440000000000007</v>
       </c>
       <c r="H966" s="8">
         <f t="shared" si="183"/>
-        <v>1991550</v>
+        <v>7910950</v>
       </c>
       <c r="I966" s="9">
-        <v>25</v>
+        <f t="shared" si="184"/>
+        <v>350</v>
       </c>
       <c r="L966" s="2">
-        <f t="shared" si="184"/>
-        <v>1991550</v>
+        <f t="shared" si="185"/>
+        <v>7910950</v>
       </c>
       <c r="M966" s="2">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>1314</v>
       </c>
       <c r="N966" s="15">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>23798.861899254214</v>
       </c>
       <c r="O966" s="15">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>39726.482706751362</v>
       </c>
       <c r="P966" s="16">
         <f>SUM($H$3:H966)</f>
-        <v>429005090</v>
+        <v>645286090</v>
       </c>
       <c r="Q966" s="2">
         <f>SUM($I$3:I966)</f>
-        <v>14374</v>
+        <v>25099</v>
       </c>
     </row>
     <row r="967" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A967" s="7">
+        <f t="shared" si="193"/>
+        <v>965</v>
+      </c>
+      <c r="B967" s="2">
+        <f t="shared" si="193"/>
+        <v>1315</v>
+      </c>
+      <c r="C967" s="14">
+        <f t="shared" si="191"/>
+        <v>23840.793864859486</v>
+      </c>
+      <c r="D967" s="14">
         <f t="shared" si="192"/>
-        <v>965</v>
-      </c>
-      <c r="B967" s="2">
-        <f t="shared" si="192"/>
-        <v>1315</v>
-      </c>
-      <c r="C967" s="14">
-        <f t="shared" si="190"/>
-        <v>23840.793864859486</v>
-      </c>
-      <c r="D967" s="14">
-        <f t="shared" si="191"/>
         <v>39802.886844429944</v>
       </c>
       <c r="E967" s="2">
         <v>1</v>
       </c>
       <c r="F967" s="2">
+        <f t="shared" si="189"/>
+        <v>9</v>
+      </c>
+      <c r="G967" s="17">
+        <f t="shared" si="190"/>
+        <v>0.38483333333333336</v>
+      </c>
+      <c r="H967" s="8">
+        <f t="shared" ref="H967:H1002" si="194">(A967-879)*93070</f>
+        <v>8004020</v>
+      </c>
+      <c r="I967" s="9">
+        <f t="shared" ref="I967:I1002" si="195">I966+5</f>
+        <v>355</v>
+      </c>
+      <c r="L967" s="2">
+        <f t="shared" si="185"/>
+        <v>8004020</v>
+      </c>
+      <c r="M967" s="2">
+        <f t="shared" si="186"/>
+        <v>1315</v>
+      </c>
+      <c r="N967" s="15">
+        <f t="shared" si="187"/>
+        <v>23840.793864859486</v>
+      </c>
+      <c r="O967" s="15">
         <f t="shared" si="188"/>
-        <v>9</v>
-      </c>
-      <c r="G967" s="17">
-        <f t="shared" si="189"/>
-        <v>0.38483333333333336</v>
-      </c>
-      <c r="H967" s="8">
-        <f t="shared" ref="H967:H1002" si="193">(A967-799)*12070</f>
-        <v>2003620</v>
-      </c>
-      <c r="I967" s="9">
-        <v>25</v>
-      </c>
-      <c r="L967" s="2">
-        <f t="shared" si="184"/>
-        <v>2003620</v>
-      </c>
-      <c r="M967" s="2">
-        <f t="shared" si="185"/>
-        <v>1315</v>
-      </c>
-      <c r="N967" s="15">
-        <f t="shared" si="186"/>
-        <v>23840.793864859486</v>
-      </c>
-      <c r="O967" s="15">
-        <f t="shared" si="187"/>
         <v>39802.886844429944</v>
       </c>
       <c r="P967" s="16">
         <f>SUM($H$3:H967)</f>
-        <v>431008710</v>
+        <v>653290110</v>
       </c>
       <c r="Q967" s="2">
         <f>SUM($I$3:I967)</f>
-        <v>14399</v>
+        <v>25454</v>
       </c>
     </row>
     <row r="968" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A968" s="7">
+        <f t="shared" si="193"/>
+        <v>966</v>
+      </c>
+      <c r="B968" s="2">
+        <f t="shared" si="193"/>
+        <v>1316</v>
+      </c>
+      <c r="C968" s="14">
+        <f t="shared" si="191"/>
+        <v>23882.738443483082</v>
+      </c>
+      <c r="D968" s="14">
         <f t="shared" si="192"/>
-        <v>966</v>
-      </c>
-      <c r="B968" s="2">
-        <f t="shared" si="192"/>
-        <v>1316</v>
-      </c>
-      <c r="C968" s="14">
-        <f t="shared" si="190"/>
-        <v>23882.738443483082</v>
-      </c>
-      <c r="D968" s="14">
-        <f t="shared" si="191"/>
         <v>39879.336953323014</v>
       </c>
       <c r="E968" s="2">
         <v>1</v>
       </c>
       <c r="F968" s="2">
+        <f t="shared" si="189"/>
+        <v>9</v>
+      </c>
+      <c r="G968" s="17">
+        <f t="shared" si="190"/>
+        <v>0.3852666666666667</v>
+      </c>
+      <c r="H968" s="8">
+        <f t="shared" si="194"/>
+        <v>8097090</v>
+      </c>
+      <c r="I968" s="9">
+        <f t="shared" si="195"/>
+        <v>360</v>
+      </c>
+      <c r="L968" s="2">
+        <f t="shared" si="185"/>
+        <v>8097090</v>
+      </c>
+      <c r="M968" s="2">
+        <f t="shared" si="186"/>
+        <v>1316</v>
+      </c>
+      <c r="N968" s="15">
+        <f t="shared" si="187"/>
+        <v>23882.738443483082</v>
+      </c>
+      <c r="O968" s="15">
         <f t="shared" si="188"/>
-        <v>9</v>
-      </c>
-      <c r="G968" s="17">
-        <f t="shared" si="189"/>
-        <v>0.3852666666666667</v>
-      </c>
-      <c r="H968" s="8">
-        <f t="shared" si="193"/>
-        <v>2015690</v>
-      </c>
-      <c r="I968" s="9">
-        <v>25</v>
-      </c>
-      <c r="L968" s="2">
-        <f t="shared" si="184"/>
-        <v>2015690</v>
-      </c>
-      <c r="M968" s="2">
-        <f t="shared" si="185"/>
-        <v>1316</v>
-      </c>
-      <c r="N968" s="15">
-        <f t="shared" si="186"/>
-        <v>23882.738443483082</v>
-      </c>
-      <c r="O968" s="15">
-        <f t="shared" si="187"/>
         <v>39879.336953323014</v>
       </c>
       <c r="P968" s="16">
         <f>SUM($H$3:H968)</f>
-        <v>433024400</v>
+        <v>661387200</v>
       </c>
       <c r="Q968" s="2">
         <f>SUM($I$3:I968)</f>
-        <v>14424</v>
+        <v>25814</v>
       </c>
     </row>
     <row r="969" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A969" s="7">
+        <f t="shared" si="193"/>
+        <v>967</v>
+      </c>
+      <c r="B969" s="2">
+        <f t="shared" si="193"/>
+        <v>1317</v>
+      </c>
+      <c r="C969" s="14">
+        <f t="shared" si="191"/>
+        <v>23924.695619971968</v>
+      </c>
+      <c r="D969" s="14">
         <f t="shared" si="192"/>
-        <v>967</v>
-      </c>
-      <c r="B969" s="2">
-        <f t="shared" si="192"/>
-        <v>1317</v>
-      </c>
-      <c r="C969" s="14">
-        <f t="shared" si="190"/>
-        <v>23924.695619971968</v>
-      </c>
-      <c r="D969" s="14">
-        <f t="shared" si="191"/>
         <v>39955.832992002557</v>
       </c>
       <c r="E969" s="2">
         <v>1</v>
       </c>
       <c r="F969" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>9</v>
       </c>
       <c r="G969" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38569999999999999</v>
       </c>
       <c r="H969" s="8">
-        <f t="shared" si="193"/>
-        <v>2027760</v>
+        <f t="shared" si="194"/>
+        <v>8190160</v>
       </c>
       <c r="I969" s="9">
-        <v>25</v>
+        <f t="shared" si="195"/>
+        <v>365</v>
       </c>
       <c r="L969" s="2">
-        <f t="shared" ref="L969:L1003" si="194">H969</f>
-        <v>2027760</v>
+        <f t="shared" ref="L969:L1003" si="196">H969</f>
+        <v>8190160</v>
       </c>
       <c r="M969" s="2">
-        <f t="shared" ref="M969:M1002" si="195">B969</f>
+        <f t="shared" ref="M969:M1002" si="197">B969</f>
         <v>1317</v>
       </c>
       <c r="N969" s="15">
-        <f t="shared" ref="N969:N1002" si="196">C969</f>
+        <f t="shared" ref="N969:N1002" si="198">C969</f>
         <v>23924.695619971968</v>
       </c>
       <c r="O969" s="15">
-        <f t="shared" ref="O969:O1002" si="197">D969</f>
+        <f t="shared" ref="O969:O1002" si="199">D969</f>
         <v>39955.832992002557</v>
       </c>
       <c r="P969" s="16">
         <f>SUM($H$3:H969)</f>
-        <v>435052160</v>
+        <v>669577360</v>
       </c>
       <c r="Q969" s="2">
         <f>SUM($I$3:I969)</f>
-        <v>14449</v>
+        <v>26179</v>
       </c>
     </row>
     <row r="970" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A970" s="7">
+        <f t="shared" si="193"/>
+        <v>968</v>
+      </c>
+      <c r="B970" s="2">
+        <f t="shared" si="193"/>
+        <v>1318</v>
+      </c>
+      <c r="C970" s="14">
+        <f t="shared" si="191"/>
+        <v>23966.665379214013</v>
+      </c>
+      <c r="D970" s="14">
         <f t="shared" si="192"/>
-        <v>968</v>
-      </c>
-      <c r="B970" s="2">
-        <f t="shared" si="192"/>
-        <v>1318</v>
-      </c>
-      <c r="C970" s="14">
-        <f t="shared" si="190"/>
-        <v>23966.665379214013</v>
-      </c>
-      <c r="D970" s="14">
-        <f t="shared" si="191"/>
         <v>40032.374919139984</v>
       </c>
       <c r="E970" s="2">
         <v>1</v>
       </c>
       <c r="F970" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>9</v>
       </c>
       <c r="G970" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38613333333333338</v>
       </c>
       <c r="H970" s="8">
-        <f t="shared" si="193"/>
-        <v>2039830</v>
+        <f t="shared" si="194"/>
+        <v>8283230</v>
       </c>
       <c r="I970" s="9">
-        <v>25</v>
+        <f t="shared" si="195"/>
+        <v>370</v>
       </c>
       <c r="L970" s="2">
-        <f t="shared" si="194"/>
-        <v>2039830</v>
+        <f t="shared" si="196"/>
+        <v>8283230</v>
       </c>
       <c r="M970" s="2">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>1318</v>
       </c>
       <c r="N970" s="15">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>23966.665379214013</v>
       </c>
       <c r="O970" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40032.374919139984</v>
       </c>
       <c r="P970" s="16">
         <f>SUM($H$3:H970)</f>
-        <v>437091990</v>
+        <v>677860590</v>
       </c>
       <c r="Q970" s="2">
         <f>SUM($I$3:I970)</f>
-        <v>14474</v>
+        <v>26549</v>
       </c>
     </row>
     <row r="971" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A971" s="7">
+        <f t="shared" si="193"/>
+        <v>969</v>
+      </c>
+      <c r="B971" s="2">
+        <f t="shared" si="193"/>
+        <v>1319</v>
+      </c>
+      <c r="C971" s="14">
+        <f t="shared" si="191"/>
+        <v>24008.647706137763</v>
+      </c>
+      <c r="D971" s="14">
         <f t="shared" si="192"/>
-        <v>969</v>
-      </c>
-      <c r="B971" s="2">
-        <f t="shared" si="192"/>
-        <v>1319</v>
-      </c>
-      <c r="C971" s="14">
-        <f t="shared" si="190"/>
-        <v>24008.647706137763</v>
-      </c>
-      <c r="D971" s="14">
-        <f t="shared" si="191"/>
         <v>40108.96269350576</v>
       </c>
       <c r="E971" s="2">
         <v>1</v>
       </c>
       <c r="F971" s="2">
-        <f t="shared" ref="F971:F1002" si="198">F951+0.2</f>
+        <f t="shared" ref="F971:F1002" si="200">F951+0.2</f>
         <v>9</v>
       </c>
       <c r="G971" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.38656666666666673</v>
       </c>
       <c r="H971" s="8">
-        <f t="shared" si="193"/>
-        <v>2051900</v>
+        <f t="shared" si="194"/>
+        <v>8376300</v>
       </c>
       <c r="I971" s="9">
-        <v>25</v>
+        <f t="shared" si="195"/>
+        <v>375</v>
       </c>
       <c r="L971" s="2">
-        <f t="shared" si="194"/>
-        <v>2051900</v>
+        <f t="shared" si="196"/>
+        <v>8376300</v>
       </c>
       <c r="M971" s="2">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>1319</v>
       </c>
       <c r="N971" s="15">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>24008.647706137763</v>
       </c>
       <c r="O971" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40108.96269350576</v>
       </c>
       <c r="P971" s="16">
         <f>SUM($H$3:H971)</f>
-        <v>439143890</v>
+        <v>686236890</v>
       </c>
       <c r="Q971" s="2">
         <f>SUM($I$3:I971)</f>
-        <v>14499</v>
+        <v>26924</v>
       </c>
     </row>
     <row r="972" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A972" s="7">
+        <f t="shared" si="193"/>
+        <v>970</v>
+      </c>
+      <c r="B972" s="2">
+        <f t="shared" si="193"/>
+        <v>1320</v>
+      </c>
+      <c r="C972" s="14">
+        <f t="shared" si="191"/>
+        <v>24050.642585712296</v>
+      </c>
+      <c r="D972" s="14">
         <f t="shared" si="192"/>
-        <v>970</v>
-      </c>
-      <c r="B972" s="2">
-        <f t="shared" si="192"/>
-        <v>1320</v>
-      </c>
-      <c r="C972" s="14">
-        <f t="shared" si="190"/>
-        <v>24050.642585712296</v>
-      </c>
-      <c r="D972" s="14">
-        <f t="shared" si="191"/>
         <v>40185.596273968949</v>
       </c>
       <c r="E972" s="2">
         <v>1</v>
       </c>
       <c r="F972" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G972" s="17">
+        <f t="shared" si="190"/>
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="H972" s="8">
+        <f t="shared" si="194"/>
+        <v>8469370</v>
+      </c>
+      <c r="I972" s="9">
+        <f t="shared" si="195"/>
+        <v>380</v>
+      </c>
+      <c r="L972" s="2">
+        <f t="shared" si="196"/>
+        <v>8469370</v>
+      </c>
+      <c r="M972" s="2">
+        <f t="shared" si="197"/>
+        <v>1320</v>
+      </c>
+      <c r="N972" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G972" s="17">
-        <f t="shared" si="189"/>
-        <v>0.38700000000000001</v>
-      </c>
-      <c r="H972" s="8">
-        <f t="shared" si="193"/>
-        <v>2063970</v>
-      </c>
-      <c r="I972" s="9">
-        <v>25</v>
-      </c>
-      <c r="L972" s="2">
-        <f t="shared" si="194"/>
-        <v>2063970</v>
-      </c>
-      <c r="M972" s="2">
-        <f t="shared" si="195"/>
-        <v>1320</v>
-      </c>
-      <c r="N972" s="15">
-        <f t="shared" si="196"/>
         <v>24050.642585712296</v>
       </c>
       <c r="O972" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40185.596273968949</v>
       </c>
       <c r="P972" s="16">
         <f>SUM($H$3:H972)</f>
-        <v>441207860</v>
+        <v>694706260</v>
       </c>
       <c r="Q972" s="2">
         <f>SUM($I$3:I972)</f>
-        <v>14524</v>
+        <v>27304</v>
       </c>
     </row>
     <row r="973" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A973" s="7">
+        <f t="shared" si="193"/>
+        <v>971</v>
+      </c>
+      <c r="B973" s="2">
+        <f t="shared" si="193"/>
+        <v>1321</v>
+      </c>
+      <c r="C973" s="14">
+        <f t="shared" si="191"/>
+        <v>24092.650002947201</v>
+      </c>
+      <c r="D973" s="14">
         <f t="shared" si="192"/>
-        <v>971</v>
-      </c>
-      <c r="B973" s="2">
-        <f t="shared" si="192"/>
-        <v>1321</v>
-      </c>
-      <c r="C973" s="14">
-        <f t="shared" si="190"/>
-        <v>24092.650002947201</v>
-      </c>
-      <c r="D973" s="14">
-        <f t="shared" si="191"/>
         <v>40262.275619496977</v>
       </c>
       <c r="E973" s="2">
         <v>1</v>
       </c>
       <c r="F973" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G973" s="17">
+        <f t="shared" si="190"/>
+        <v>0.38743333333333335</v>
+      </c>
+      <c r="H973" s="8">
+        <f t="shared" si="194"/>
+        <v>8562440</v>
+      </c>
+      <c r="I973" s="9">
+        <f t="shared" si="195"/>
+        <v>385</v>
+      </c>
+      <c r="L973" s="2">
+        <f t="shared" si="196"/>
+        <v>8562440</v>
+      </c>
+      <c r="M973" s="2">
+        <f t="shared" si="197"/>
+        <v>1321</v>
+      </c>
+      <c r="N973" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G973" s="17">
-        <f t="shared" si="189"/>
-        <v>0.38743333333333335</v>
-      </c>
-      <c r="H973" s="8">
-        <f t="shared" si="193"/>
-        <v>2076040</v>
-      </c>
-      <c r="I973" s="9">
-        <v>25</v>
-      </c>
-      <c r="L973" s="2">
-        <f t="shared" si="194"/>
-        <v>2076040</v>
-      </c>
-      <c r="M973" s="2">
-        <f t="shared" si="195"/>
-        <v>1321</v>
-      </c>
-      <c r="N973" s="15">
-        <f t="shared" si="196"/>
         <v>24092.650002947201</v>
       </c>
       <c r="O973" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40262.275619496977</v>
       </c>
       <c r="P973" s="16">
         <f>SUM($H$3:H973)</f>
-        <v>443283900</v>
+        <v>703268700</v>
       </c>
       <c r="Q973" s="2">
         <f>SUM($I$3:I973)</f>
-        <v>14549</v>
+        <v>27689</v>
       </c>
     </row>
     <row r="974" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A974" s="7">
+        <f t="shared" si="193"/>
+        <v>972</v>
+      </c>
+      <c r="B974" s="2">
+        <f t="shared" si="193"/>
+        <v>1322</v>
+      </c>
+      <c r="C974" s="14">
+        <f t="shared" si="191"/>
+        <v>24134.669942892167</v>
+      </c>
+      <c r="D974" s="14">
         <f t="shared" si="192"/>
-        <v>972</v>
-      </c>
-      <c r="B974" s="2">
-        <f t="shared" si="192"/>
-        <v>1322</v>
-      </c>
-      <c r="C974" s="14">
-        <f t="shared" si="190"/>
-        <v>24134.669942892167</v>
-      </c>
-      <c r="D974" s="14">
-        <f t="shared" si="191"/>
         <v>40339.000689154935</v>
       </c>
       <c r="E974" s="2">
         <v>1</v>
       </c>
       <c r="F974" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G974" s="17">
+        <f t="shared" si="190"/>
+        <v>0.38786666666666664</v>
+      </c>
+      <c r="H974" s="8">
+        <f t="shared" si="194"/>
+        <v>8655510</v>
+      </c>
+      <c r="I974" s="9">
+        <f t="shared" si="195"/>
+        <v>390</v>
+      </c>
+      <c r="L974" s="2">
+        <f t="shared" si="196"/>
+        <v>8655510</v>
+      </c>
+      <c r="M974" s="2">
+        <f t="shared" si="197"/>
+        <v>1322</v>
+      </c>
+      <c r="N974" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G974" s="17">
-        <f t="shared" si="189"/>
-        <v>0.38786666666666664</v>
-      </c>
-      <c r="H974" s="8">
-        <f t="shared" si="193"/>
-        <v>2088110</v>
-      </c>
-      <c r="I974" s="9">
-        <v>25</v>
-      </c>
-      <c r="L974" s="2">
-        <f t="shared" si="194"/>
-        <v>2088110</v>
-      </c>
-      <c r="M974" s="2">
-        <f t="shared" si="195"/>
-        <v>1322</v>
-      </c>
-      <c r="N974" s="15">
-        <f t="shared" si="196"/>
         <v>24134.669942892167</v>
       </c>
       <c r="O974" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40339.000689154935</v>
       </c>
       <c r="P974" s="16">
         <f>SUM($H$3:H974)</f>
-        <v>445372010</v>
+        <v>711924210</v>
       </c>
       <c r="Q974" s="2">
         <f>SUM($I$3:I974)</f>
-        <v>14574</v>
+        <v>28079</v>
       </c>
     </row>
     <row r="975" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A975" s="7">
+        <f t="shared" si="193"/>
+        <v>973</v>
+      </c>
+      <c r="B975" s="2">
+        <f t="shared" si="193"/>
+        <v>1323</v>
+      </c>
+      <c r="C975" s="14">
+        <f t="shared" si="191"/>
+        <v>24176.702390636976</v>
+      </c>
+      <c r="D975" s="14">
         <f t="shared" si="192"/>
-        <v>973</v>
-      </c>
-      <c r="B975" s="2">
-        <f t="shared" si="192"/>
-        <v>1323</v>
-      </c>
-      <c r="C975" s="14">
-        <f t="shared" si="190"/>
-        <v>24176.702390636976</v>
-      </c>
-      <c r="D975" s="14">
-        <f t="shared" si="191"/>
         <v>40415.771442105521</v>
       </c>
       <c r="E975" s="2">
         <v>1</v>
       </c>
       <c r="F975" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G975" s="17">
+        <f t="shared" si="190"/>
+        <v>0.38830000000000003</v>
+      </c>
+      <c r="H975" s="8">
+        <f t="shared" si="194"/>
+        <v>8748580</v>
+      </c>
+      <c r="I975" s="9">
+        <f t="shared" si="195"/>
+        <v>395</v>
+      </c>
+      <c r="L975" s="2">
+        <f t="shared" si="196"/>
+        <v>8748580</v>
+      </c>
+      <c r="M975" s="2">
+        <f t="shared" si="197"/>
+        <v>1323</v>
+      </c>
+      <c r="N975" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G975" s="17">
-        <f t="shared" si="189"/>
-        <v>0.38830000000000003</v>
-      </c>
-      <c r="H975" s="8">
-        <f t="shared" si="193"/>
-        <v>2100180</v>
-      </c>
-      <c r="I975" s="9">
-        <v>25</v>
-      </c>
-      <c r="L975" s="2">
-        <f t="shared" si="194"/>
-        <v>2100180</v>
-      </c>
-      <c r="M975" s="2">
-        <f t="shared" si="195"/>
-        <v>1323</v>
-      </c>
-      <c r="N975" s="15">
-        <f t="shared" si="196"/>
         <v>24176.702390636976</v>
       </c>
       <c r="O975" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40415.771442105521</v>
       </c>
       <c r="P975" s="16">
         <f>SUM($H$3:H975)</f>
-        <v>447472190</v>
+        <v>720672790</v>
       </c>
       <c r="Q975" s="2">
         <f>SUM($I$3:I975)</f>
-        <v>14599</v>
+        <v>28474</v>
       </c>
     </row>
     <row r="976" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A976" s="7">
+        <f t="shared" si="193"/>
+        <v>974</v>
+      </c>
+      <c r="B976" s="2">
+        <f t="shared" si="193"/>
+        <v>1324</v>
+      </c>
+      <c r="C976" s="14">
+        <f t="shared" si="191"/>
+        <v>24218.747331311304</v>
+      </c>
+      <c r="D976" s="14">
         <f t="shared" si="192"/>
-        <v>974</v>
-      </c>
-      <c r="B976" s="2">
-        <f t="shared" si="192"/>
-        <v>1324</v>
-      </c>
-      <c r="C976" s="14">
-        <f t="shared" si="190"/>
-        <v>24218.747331311304</v>
-      </c>
-      <c r="D976" s="14">
-        <f t="shared" si="191"/>
         <v>40492.587837608691</v>
       </c>
       <c r="E976" s="2">
         <v>1</v>
       </c>
       <c r="F976" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G976" s="17">
+        <f t="shared" si="190"/>
+        <v>0.38873333333333338</v>
+      </c>
+      <c r="H976" s="8">
+        <f t="shared" si="194"/>
+        <v>8841650</v>
+      </c>
+      <c r="I976" s="9">
+        <f t="shared" si="195"/>
+        <v>400</v>
+      </c>
+      <c r="L976" s="2">
+        <f t="shared" si="196"/>
+        <v>8841650</v>
+      </c>
+      <c r="M976" s="2">
+        <f t="shared" si="197"/>
+        <v>1324</v>
+      </c>
+      <c r="N976" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G976" s="17">
-        <f t="shared" si="189"/>
-        <v>0.38873333333333338</v>
-      </c>
-      <c r="H976" s="8">
-        <f t="shared" si="193"/>
-        <v>2112250</v>
-      </c>
-      <c r="I976" s="9">
-        <v>25</v>
-      </c>
-      <c r="L976" s="2">
-        <f t="shared" si="194"/>
-        <v>2112250</v>
-      </c>
-      <c r="M976" s="2">
-        <f t="shared" si="195"/>
-        <v>1324</v>
-      </c>
-      <c r="N976" s="15">
-        <f t="shared" si="196"/>
         <v>24218.747331311304</v>
       </c>
       <c r="O976" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40492.587837608691</v>
       </c>
       <c r="P976" s="16">
         <f>SUM($H$3:H976)</f>
-        <v>449584440</v>
+        <v>729514440</v>
       </c>
       <c r="Q976" s="2">
         <f>SUM($I$3:I976)</f>
-        <v>14624</v>
+        <v>28874</v>
       </c>
     </row>
     <row r="977" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A977" s="7">
+        <f t="shared" si="193"/>
+        <v>975</v>
+      </c>
+      <c r="B977" s="2">
+        <f t="shared" si="193"/>
+        <v>1325</v>
+      </c>
+      <c r="C977" s="14">
+        <f t="shared" si="191"/>
+        <v>24260.804750084535</v>
+      </c>
+      <c r="D977" s="14">
         <f t="shared" si="192"/>
-        <v>975</v>
-      </c>
-      <c r="B977" s="2">
-        <f t="shared" si="192"/>
-        <v>1325</v>
-      </c>
-      <c r="C977" s="14">
-        <f t="shared" si="190"/>
-        <v>24260.804750084535</v>
-      </c>
-      <c r="D977" s="14">
-        <f t="shared" si="191"/>
         <v>40569.449835020867</v>
       </c>
       <c r="E977" s="2">
         <v>1</v>
       </c>
       <c r="F977" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G977" s="17">
+        <f t="shared" si="190"/>
+        <v>0.38916666666666666</v>
+      </c>
+      <c r="H977" s="8">
+        <f t="shared" si="194"/>
+        <v>8934720</v>
+      </c>
+      <c r="I977" s="9">
+        <f t="shared" si="195"/>
+        <v>405</v>
+      </c>
+      <c r="L977" s="2">
+        <f t="shared" si="196"/>
+        <v>8934720</v>
+      </c>
+      <c r="M977" s="2">
+        <f t="shared" si="197"/>
+        <v>1325</v>
+      </c>
+      <c r="N977" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G977" s="17">
-        <f t="shared" si="189"/>
-        <v>0.38916666666666666</v>
-      </c>
-      <c r="H977" s="8">
-        <f t="shared" si="193"/>
-        <v>2124320</v>
-      </c>
-      <c r="I977" s="9">
-        <v>25</v>
-      </c>
-      <c r="L977" s="2">
-        <f t="shared" si="194"/>
-        <v>2124320</v>
-      </c>
-      <c r="M977" s="2">
-        <f t="shared" si="195"/>
-        <v>1325</v>
-      </c>
-      <c r="N977" s="15">
-        <f t="shared" si="196"/>
         <v>24260.804750084535</v>
       </c>
       <c r="O977" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40569.449835020867</v>
       </c>
       <c r="P977" s="16">
         <f>SUM($H$3:H977)</f>
-        <v>451708760</v>
+        <v>738449160</v>
       </c>
       <c r="Q977" s="2">
         <f>SUM($I$3:I977)</f>
-        <v>14649</v>
+        <v>29279</v>
       </c>
     </row>
     <row r="978" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A978" s="7">
+        <f t="shared" si="193"/>
+        <v>976</v>
+      </c>
+      <c r="B978" s="2">
+        <f t="shared" si="193"/>
+        <v>1326</v>
+      </c>
+      <c r="C978" s="14">
+        <f t="shared" si="191"/>
+        <v>24302.874632165614</v>
+      </c>
+      <c r="D978" s="14">
         <f t="shared" si="192"/>
-        <v>976</v>
-      </c>
-      <c r="B978" s="2">
-        <f t="shared" si="192"/>
-        <v>1326</v>
-      </c>
-      <c r="C978" s="14">
-        <f t="shared" si="190"/>
-        <v>24302.874632165614</v>
-      </c>
-      <c r="D978" s="14">
-        <f t="shared" si="191"/>
         <v>40646.357393795013</v>
       </c>
       <c r="E978" s="2">
         <v>1</v>
       </c>
       <c r="F978" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G978" s="17">
+        <f t="shared" si="190"/>
+        <v>0.3896</v>
+      </c>
+      <c r="H978" s="8">
+        <f t="shared" si="194"/>
+        <v>9027790</v>
+      </c>
+      <c r="I978" s="9">
+        <f t="shared" si="195"/>
+        <v>410</v>
+      </c>
+      <c r="L978" s="2">
+        <f t="shared" si="196"/>
+        <v>9027790</v>
+      </c>
+      <c r="M978" s="2">
+        <f t="shared" si="197"/>
+        <v>1326</v>
+      </c>
+      <c r="N978" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G978" s="17">
-        <f t="shared" si="189"/>
-        <v>0.3896</v>
-      </c>
-      <c r="H978" s="8">
-        <f t="shared" si="193"/>
-        <v>2136390</v>
-      </c>
-      <c r="I978" s="9">
-        <v>25</v>
-      </c>
-      <c r="L978" s="2">
-        <f t="shared" si="194"/>
-        <v>2136390</v>
-      </c>
-      <c r="M978" s="2">
-        <f t="shared" si="195"/>
-        <v>1326</v>
-      </c>
-      <c r="N978" s="15">
-        <f t="shared" si="196"/>
         <v>24302.874632165614</v>
       </c>
       <c r="O978" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40646.357393795013</v>
       </c>
       <c r="P978" s="16">
         <f>SUM($H$3:H978)</f>
-        <v>453845150</v>
+        <v>747476950</v>
       </c>
       <c r="Q978" s="2">
         <f>SUM($I$3:I978)</f>
-        <v>14674</v>
+        <v>29689</v>
       </c>
     </row>
     <row r="979" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A979" s="7">
+        <f t="shared" si="193"/>
+        <v>977</v>
+      </c>
+      <c r="B979" s="2">
+        <f t="shared" si="193"/>
+        <v>1327</v>
+      </c>
+      <c r="C979" s="14">
+        <f t="shared" si="191"/>
+        <v>24344.956962802844</v>
+      </c>
+      <c r="D979" s="14">
         <f t="shared" si="192"/>
-        <v>977</v>
-      </c>
-      <c r="B979" s="2">
-        <f t="shared" si="192"/>
-        <v>1327</v>
-      </c>
-      <c r="C979" s="14">
-        <f t="shared" si="190"/>
-        <v>24344.956962802844</v>
-      </c>
-      <c r="D979" s="14">
-        <f t="shared" si="191"/>
         <v>40723.310473480116</v>
       </c>
       <c r="E979" s="2">
         <v>1</v>
       </c>
       <c r="F979" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G979" s="17">
+        <f t="shared" si="190"/>
+        <v>0.3900333333333334</v>
+      </c>
+      <c r="H979" s="8">
+        <f t="shared" si="194"/>
+        <v>9120860</v>
+      </c>
+      <c r="I979" s="9">
+        <f t="shared" si="195"/>
+        <v>415</v>
+      </c>
+      <c r="L979" s="2">
+        <f t="shared" si="196"/>
+        <v>9120860</v>
+      </c>
+      <c r="M979" s="2">
+        <f t="shared" si="197"/>
+        <v>1327</v>
+      </c>
+      <c r="N979" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G979" s="17">
-        <f t="shared" si="189"/>
-        <v>0.3900333333333334</v>
-      </c>
-      <c r="H979" s="8">
-        <f t="shared" si="193"/>
-        <v>2148460</v>
-      </c>
-      <c r="I979" s="9">
-        <v>25</v>
-      </c>
-      <c r="L979" s="2">
-        <f t="shared" si="194"/>
-        <v>2148460</v>
-      </c>
-      <c r="M979" s="2">
-        <f t="shared" si="195"/>
-        <v>1327</v>
-      </c>
-      <c r="N979" s="15">
-        <f t="shared" si="196"/>
         <v>24344.956962802844</v>
       </c>
       <c r="O979" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40723.310473480116</v>
       </c>
       <c r="P979" s="16">
         <f>SUM($H$3:H979)</f>
-        <v>455993610</v>
+        <v>756597810</v>
       </c>
       <c r="Q979" s="2">
         <f>SUM($I$3:I979)</f>
-        <v>14699</v>
+        <v>30104</v>
       </c>
     </row>
     <row r="980" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A980" s="7">
+        <f t="shared" si="193"/>
+        <v>978</v>
+      </c>
+      <c r="B980" s="2">
+        <f t="shared" si="193"/>
+        <v>1328</v>
+      </c>
+      <c r="C980" s="14">
+        <f t="shared" si="191"/>
+        <v>24387.051727283815</v>
+      </c>
+      <c r="D980" s="14">
         <f t="shared" si="192"/>
-        <v>978</v>
-      </c>
-      <c r="B980" s="2">
-        <f t="shared" si="192"/>
-        <v>1328</v>
-      </c>
-      <c r="C980" s="14">
-        <f t="shared" si="190"/>
-        <v>24387.051727283815</v>
-      </c>
-      <c r="D980" s="14">
-        <f t="shared" si="191"/>
         <v>40800.309033720616</v>
       </c>
       <c r="E980" s="2">
         <v>1</v>
       </c>
       <c r="F980" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G980" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39046666666666668</v>
+      </c>
+      <c r="H980" s="8">
+        <f t="shared" si="194"/>
+        <v>9213930</v>
+      </c>
+      <c r="I980" s="9">
+        <f t="shared" si="195"/>
+        <v>420</v>
+      </c>
+      <c r="L980" s="2">
+        <f t="shared" si="196"/>
+        <v>9213930</v>
+      </c>
+      <c r="M980" s="2">
+        <f t="shared" si="197"/>
+        <v>1328</v>
+      </c>
+      <c r="N980" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G980" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39046666666666668</v>
-      </c>
-      <c r="H980" s="8">
-        <f t="shared" si="193"/>
-        <v>2160530</v>
-      </c>
-      <c r="I980" s="9">
-        <v>25</v>
-      </c>
-      <c r="L980" s="2">
-        <f t="shared" si="194"/>
-        <v>2160530</v>
-      </c>
-      <c r="M980" s="2">
-        <f t="shared" si="195"/>
-        <v>1328</v>
-      </c>
-      <c r="N980" s="15">
-        <f t="shared" si="196"/>
         <v>24387.051727283815</v>
       </c>
       <c r="O980" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40800.309033720616</v>
       </c>
       <c r="P980" s="16">
         <f>SUM($H$3:H980)</f>
-        <v>458154140</v>
+        <v>765811740</v>
       </c>
       <c r="Q980" s="2">
         <f>SUM($I$3:I980)</f>
-        <v>14724</v>
+        <v>30524</v>
       </c>
     </row>
     <row r="981" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A981" s="7">
+        <f t="shared" si="193"/>
+        <v>979</v>
+      </c>
+      <c r="B981" s="2">
+        <f t="shared" si="193"/>
+        <v>1329</v>
+      </c>
+      <c r="C981" s="14">
+        <f t="shared" si="191"/>
+        <v>24429.158910935148</v>
+      </c>
+      <c r="D981" s="14">
         <f t="shared" si="192"/>
-        <v>979</v>
-      </c>
-      <c r="B981" s="2">
-        <f t="shared" si="192"/>
-        <v>1329</v>
-      </c>
-      <c r="C981" s="14">
-        <f t="shared" si="190"/>
-        <v>24429.158910935148</v>
-      </c>
-      <c r="D981" s="14">
-        <f t="shared" si="191"/>
         <v>40877.353034256426</v>
       </c>
       <c r="E981" s="2">
         <v>1</v>
       </c>
       <c r="F981" s="2">
+        <f t="shared" si="200"/>
+        <v>9</v>
+      </c>
+      <c r="G981" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39090000000000003</v>
+      </c>
+      <c r="H981" s="8">
+        <f t="shared" si="194"/>
+        <v>9307000</v>
+      </c>
+      <c r="I981" s="9">
+        <f t="shared" si="195"/>
+        <v>425</v>
+      </c>
+      <c r="L981" s="2">
+        <f t="shared" si="196"/>
+        <v>9307000</v>
+      </c>
+      <c r="M981" s="2">
+        <f t="shared" si="197"/>
+        <v>1329</v>
+      </c>
+      <c r="N981" s="15">
         <f t="shared" si="198"/>
-        <v>9</v>
-      </c>
-      <c r="G981" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39090000000000003</v>
-      </c>
-      <c r="H981" s="8">
-        <f t="shared" si="193"/>
-        <v>2172600</v>
-      </c>
-      <c r="I981" s="9">
-        <v>25</v>
-      </c>
-      <c r="L981" s="2">
-        <f t="shared" si="194"/>
-        <v>2172600</v>
-      </c>
-      <c r="M981" s="2">
-        <f t="shared" si="195"/>
-        <v>1329</v>
-      </c>
-      <c r="N981" s="15">
-        <f t="shared" si="196"/>
         <v>24429.158910935148</v>
       </c>
       <c r="O981" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40877.353034256426</v>
       </c>
       <c r="P981" s="16">
         <f>SUM($H$3:H981)</f>
-        <v>460326740</v>
+        <v>775118740</v>
       </c>
       <c r="Q981" s="2">
         <f>SUM($I$3:I981)</f>
-        <v>14749</v>
+        <v>30949</v>
       </c>
     </row>
     <row r="982" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A982" s="7">
+        <f t="shared" si="193"/>
+        <v>980</v>
+      </c>
+      <c r="B982" s="2">
+        <f t="shared" si="193"/>
+        <v>1330</v>
+      </c>
+      <c r="C982" s="14">
+        <f t="shared" si="191"/>
+        <v>24471.278499122342</v>
+      </c>
+      <c r="D982" s="14">
         <f t="shared" si="192"/>
-        <v>980</v>
-      </c>
-      <c r="B982" s="2">
-        <f t="shared" si="192"/>
-        <v>1330</v>
-      </c>
-      <c r="C982" s="14">
-        <f t="shared" si="190"/>
-        <v>24471.278499122342</v>
-      </c>
-      <c r="D982" s="14">
-        <f t="shared" si="191"/>
         <v>40954.442434922217</v>
       </c>
       <c r="E982" s="2">
         <v>1</v>
       </c>
       <c r="F982" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G982" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39133333333333331</v>
+      </c>
+      <c r="H982" s="8">
+        <f t="shared" si="194"/>
+        <v>9400070</v>
+      </c>
+      <c r="I982" s="9">
+        <f t="shared" si="195"/>
+        <v>430</v>
+      </c>
+      <c r="L982" s="2">
+        <f t="shared" si="196"/>
+        <v>9400070</v>
+      </c>
+      <c r="M982" s="2">
+        <f t="shared" si="197"/>
+        <v>1330</v>
+      </c>
+      <c r="N982" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G982" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39133333333333331</v>
-      </c>
-      <c r="H982" s="8">
-        <f t="shared" si="193"/>
-        <v>2184670</v>
-      </c>
-      <c r="I982" s="9">
-        <v>25</v>
-      </c>
-      <c r="L982" s="2">
-        <f t="shared" si="194"/>
-        <v>2184670</v>
-      </c>
-      <c r="M982" s="2">
-        <f t="shared" si="195"/>
-        <v>1330</v>
-      </c>
-      <c r="N982" s="15">
-        <f t="shared" si="196"/>
         <v>24471.278499122342</v>
       </c>
       <c r="O982" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>40954.442434922217</v>
       </c>
       <c r="P982" s="16">
         <f>SUM($H$3:H982)</f>
-        <v>462511410</v>
+        <v>784518810</v>
       </c>
       <c r="Q982" s="2">
         <f>SUM($I$3:I982)</f>
-        <v>14774</v>
+        <v>31379</v>
       </c>
     </row>
     <row r="983" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A983" s="7">
+        <f t="shared" si="193"/>
+        <v>981</v>
+      </c>
+      <c r="B983" s="2">
+        <f t="shared" si="193"/>
+        <v>1331</v>
+      </c>
+      <c r="C983" s="14">
+        <f t="shared" si="191"/>
+        <v>24513.410477249701</v>
+      </c>
+      <c r="D983" s="14">
         <f t="shared" si="192"/>
-        <v>981</v>
-      </c>
-      <c r="B983" s="2">
-        <f t="shared" si="192"/>
-        <v>1331</v>
-      </c>
-      <c r="C983" s="14">
-        <f t="shared" si="190"/>
-        <v>24513.410477249701</v>
-      </c>
-      <c r="D983" s="14">
-        <f t="shared" si="191"/>
         <v>41031.577195647245</v>
       </c>
       <c r="E983" s="2">
         <v>1</v>
       </c>
       <c r="F983" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G983" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39176666666666671</v>
+      </c>
+      <c r="H983" s="8">
+        <f t="shared" si="194"/>
+        <v>9493140</v>
+      </c>
+      <c r="I983" s="9">
+        <f t="shared" si="195"/>
+        <v>435</v>
+      </c>
+      <c r="L983" s="2">
+        <f t="shared" si="196"/>
+        <v>9493140</v>
+      </c>
+      <c r="M983" s="2">
+        <f t="shared" si="197"/>
+        <v>1331</v>
+      </c>
+      <c r="N983" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G983" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39176666666666671</v>
-      </c>
-      <c r="H983" s="8">
-        <f t="shared" si="193"/>
-        <v>2196740</v>
-      </c>
-      <c r="I983" s="9">
-        <v>25</v>
-      </c>
-      <c r="L983" s="2">
-        <f t="shared" si="194"/>
-        <v>2196740</v>
-      </c>
-      <c r="M983" s="2">
-        <f t="shared" si="195"/>
-        <v>1331</v>
-      </c>
-      <c r="N983" s="15">
-        <f t="shared" si="196"/>
         <v>24513.410477249701</v>
       </c>
       <c r="O983" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41031.577195647245</v>
       </c>
       <c r="P983" s="16">
         <f>SUM($H$3:H983)</f>
-        <v>464708150</v>
+        <v>794011950</v>
       </c>
       <c r="Q983" s="2">
         <f>SUM($I$3:I983)</f>
-        <v>14799</v>
+        <v>31814</v>
       </c>
     </row>
     <row r="984" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A984" s="7">
+        <f t="shared" si="193"/>
+        <v>982</v>
+      </c>
+      <c r="B984" s="2">
+        <f t="shared" si="193"/>
+        <v>1332</v>
+      </c>
+      <c r="C984" s="14">
+        <f t="shared" si="191"/>
+        <v>24555.554830760091</v>
+      </c>
+      <c r="D984" s="14">
         <f t="shared" si="192"/>
-        <v>982</v>
-      </c>
-      <c r="B984" s="2">
-        <f t="shared" si="192"/>
-        <v>1332</v>
-      </c>
-      <c r="C984" s="14">
-        <f t="shared" si="190"/>
-        <v>24555.554830760091</v>
-      </c>
-      <c r="D984" s="14">
-        <f t="shared" si="191"/>
         <v>41108.757276454984</v>
       </c>
       <c r="E984" s="2">
         <v>1</v>
       </c>
       <c r="F984" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G984" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39220000000000005</v>
+      </c>
+      <c r="H984" s="8">
+        <f t="shared" si="194"/>
+        <v>9586210</v>
+      </c>
+      <c r="I984" s="9">
+        <f t="shared" si="195"/>
+        <v>440</v>
+      </c>
+      <c r="L984" s="2">
+        <f t="shared" si="196"/>
+        <v>9586210</v>
+      </c>
+      <c r="M984" s="2">
+        <f t="shared" si="197"/>
+        <v>1332</v>
+      </c>
+      <c r="N984" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G984" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39220000000000005</v>
-      </c>
-      <c r="H984" s="8">
-        <f t="shared" si="193"/>
-        <v>2208810</v>
-      </c>
-      <c r="I984" s="9">
-        <v>25</v>
-      </c>
-      <c r="L984" s="2">
-        <f t="shared" si="194"/>
-        <v>2208810</v>
-      </c>
-      <c r="M984" s="2">
-        <f t="shared" si="195"/>
-        <v>1332</v>
-      </c>
-      <c r="N984" s="15">
-        <f t="shared" si="196"/>
         <v>24555.554830760091</v>
       </c>
       <c r="O984" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41108.757276454984</v>
       </c>
       <c r="P984" s="16">
         <f>SUM($H$3:H984)</f>
-        <v>466916960</v>
+        <v>803598160</v>
       </c>
       <c r="Q984" s="2">
         <f>SUM($I$3:I984)</f>
-        <v>14824</v>
+        <v>32254</v>
       </c>
     </row>
     <row r="985" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A985" s="7">
+        <f t="shared" si="193"/>
+        <v>983</v>
+      </c>
+      <c r="B985" s="2">
+        <f t="shared" si="193"/>
+        <v>1333</v>
+      </c>
+      <c r="C985" s="14">
+        <f t="shared" si="191"/>
+        <v>24597.711545134756</v>
+      </c>
+      <c r="D985" s="14">
         <f t="shared" si="192"/>
-        <v>983</v>
-      </c>
-      <c r="B985" s="2">
-        <f t="shared" si="192"/>
-        <v>1333</v>
-      </c>
-      <c r="C985" s="14">
-        <f t="shared" si="190"/>
-        <v>24597.711545134756</v>
-      </c>
-      <c r="D985" s="14">
-        <f t="shared" si="191"/>
         <v>41185.982637462585</v>
       </c>
       <c r="E985" s="2">
         <v>1</v>
       </c>
       <c r="F985" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G985" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39263333333333333</v>
+      </c>
+      <c r="H985" s="8">
+        <f t="shared" si="194"/>
+        <v>9679280</v>
+      </c>
+      <c r="I985" s="9">
+        <f t="shared" si="195"/>
+        <v>445</v>
+      </c>
+      <c r="L985" s="2">
+        <f t="shared" si="196"/>
+        <v>9679280</v>
+      </c>
+      <c r="M985" s="2">
+        <f t="shared" si="197"/>
+        <v>1333</v>
+      </c>
+      <c r="N985" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G985" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39263333333333333</v>
-      </c>
-      <c r="H985" s="8">
-        <f t="shared" si="193"/>
-        <v>2220880</v>
-      </c>
-      <c r="I985" s="9">
-        <v>25</v>
-      </c>
-      <c r="L985" s="2">
-        <f t="shared" si="194"/>
-        <v>2220880</v>
-      </c>
-      <c r="M985" s="2">
-        <f t="shared" si="195"/>
-        <v>1333</v>
-      </c>
-      <c r="N985" s="15">
-        <f t="shared" si="196"/>
         <v>24597.711545134756</v>
       </c>
       <c r="O985" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41185.982637462585</v>
       </c>
       <c r="P985" s="16">
         <f>SUM($H$3:H985)</f>
-        <v>469137840</v>
+        <v>813277440</v>
       </c>
       <c r="Q985" s="2">
         <f>SUM($I$3:I985)</f>
-        <v>14849</v>
+        <v>32699</v>
       </c>
     </row>
     <row r="986" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A986" s="7">
+        <f t="shared" si="193"/>
+        <v>984</v>
+      </c>
+      <c r="B986" s="2">
+        <f t="shared" si="193"/>
+        <v>1334</v>
+      </c>
+      <c r="C986" s="14">
+        <f t="shared" si="191"/>
+        <v>24639.880605893239</v>
+      </c>
+      <c r="D986" s="14">
         <f t="shared" si="192"/>
-        <v>984</v>
-      </c>
-      <c r="B986" s="2">
-        <f t="shared" si="192"/>
-        <v>1334</v>
-      </c>
-      <c r="C986" s="14">
-        <f t="shared" si="190"/>
-        <v>24639.880605893239</v>
-      </c>
-      <c r="D986" s="14">
-        <f t="shared" si="191"/>
         <v>41263.25323888073</v>
       </c>
       <c r="E986" s="2">
         <v>1</v>
       </c>
       <c r="F986" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G986" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39306666666666668</v>
+      </c>
+      <c r="H986" s="8">
+        <f t="shared" si="194"/>
+        <v>9772350</v>
+      </c>
+      <c r="I986" s="9">
+        <f t="shared" si="195"/>
+        <v>450</v>
+      </c>
+      <c r="L986" s="2">
+        <f t="shared" si="196"/>
+        <v>9772350</v>
+      </c>
+      <c r="M986" s="2">
+        <f t="shared" si="197"/>
+        <v>1334</v>
+      </c>
+      <c r="N986" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G986" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39306666666666668</v>
-      </c>
-      <c r="H986" s="8">
-        <f t="shared" si="193"/>
-        <v>2232950</v>
-      </c>
-      <c r="I986" s="9">
-        <v>25</v>
-      </c>
-      <c r="L986" s="2">
-        <f t="shared" si="194"/>
-        <v>2232950</v>
-      </c>
-      <c r="M986" s="2">
-        <f t="shared" si="195"/>
-        <v>1334</v>
-      </c>
-      <c r="N986" s="15">
-        <f t="shared" si="196"/>
         <v>24639.880605893239</v>
       </c>
       <c r="O986" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41263.25323888073</v>
       </c>
       <c r="P986" s="16">
         <f>SUM($H$3:H986)</f>
-        <v>471370790</v>
+        <v>823049790</v>
       </c>
       <c r="Q986" s="2">
         <f>SUM($I$3:I986)</f>
-        <v>14874</v>
+        <v>33149</v>
       </c>
     </row>
     <row r="987" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A987" s="7">
+        <f t="shared" si="193"/>
+        <v>985</v>
+      </c>
+      <c r="B987" s="2">
+        <f t="shared" si="193"/>
+        <v>1335</v>
+      </c>
+      <c r="C987" s="14">
+        <f t="shared" si="191"/>
+        <v>24682.061998593268</v>
+      </c>
+      <c r="D987" s="14">
         <f t="shared" si="192"/>
-        <v>985</v>
-      </c>
-      <c r="B987" s="2">
-        <f t="shared" si="192"/>
-        <v>1335</v>
-      </c>
-      <c r="C987" s="14">
-        <f t="shared" si="190"/>
-        <v>24682.061998593268</v>
-      </c>
-      <c r="D987" s="14">
-        <f t="shared" si="191"/>
         <v>41340.569041013296</v>
       </c>
       <c r="E987" s="2">
         <v>1</v>
       </c>
       <c r="F987" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G987" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39350000000000007</v>
+      </c>
+      <c r="H987" s="8">
+        <f t="shared" si="194"/>
+        <v>9865420</v>
+      </c>
+      <c r="I987" s="9">
+        <f t="shared" si="195"/>
+        <v>455</v>
+      </c>
+      <c r="L987" s="2">
+        <f t="shared" si="196"/>
+        <v>9865420</v>
+      </c>
+      <c r="M987" s="2">
+        <f t="shared" si="197"/>
+        <v>1335</v>
+      </c>
+      <c r="N987" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G987" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39350000000000007</v>
-      </c>
-      <c r="H987" s="8">
-        <f t="shared" si="193"/>
-        <v>2245020</v>
-      </c>
-      <c r="I987" s="9">
-        <v>25</v>
-      </c>
-      <c r="L987" s="2">
-        <f t="shared" si="194"/>
-        <v>2245020</v>
-      </c>
-      <c r="M987" s="2">
-        <f t="shared" si="195"/>
-        <v>1335</v>
-      </c>
-      <c r="N987" s="15">
-        <f t="shared" si="196"/>
         <v>24682.061998593268</v>
       </c>
       <c r="O987" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41340.569041013296</v>
       </c>
       <c r="P987" s="16">
         <f>SUM($H$3:H987)</f>
-        <v>473615810</v>
+        <v>832915210</v>
       </c>
       <c r="Q987" s="2">
         <f>SUM($I$3:I987)</f>
-        <v>14899</v>
+        <v>33604</v>
       </c>
     </row>
     <row r="988" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A988" s="7">
+        <f t="shared" si="193"/>
+        <v>986</v>
+      </c>
+      <c r="B988" s="2">
+        <f t="shared" si="193"/>
+        <v>1336</v>
+      </c>
+      <c r="C988" s="14">
+        <f t="shared" si="191"/>
+        <v>24724.255708830398</v>
+      </c>
+      <c r="D988" s="14">
         <f t="shared" si="192"/>
-        <v>986</v>
-      </c>
-      <c r="B988" s="2">
-        <f t="shared" si="192"/>
-        <v>1336</v>
-      </c>
-      <c r="C988" s="14">
-        <f t="shared" si="190"/>
-        <v>24724.255708830398</v>
-      </c>
-      <c r="D988" s="14">
-        <f t="shared" si="191"/>
         <v>41417.930004256777</v>
       </c>
       <c r="E988" s="2">
         <v>1</v>
       </c>
       <c r="F988" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G988" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39393333333333336</v>
+      </c>
+      <c r="H988" s="8">
+        <f t="shared" si="194"/>
+        <v>9958490</v>
+      </c>
+      <c r="I988" s="9">
+        <f t="shared" si="195"/>
+        <v>460</v>
+      </c>
+      <c r="L988" s="2">
+        <f t="shared" si="196"/>
+        <v>9958490</v>
+      </c>
+      <c r="M988" s="2">
+        <f t="shared" si="197"/>
+        <v>1336</v>
+      </c>
+      <c r="N988" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G988" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39393333333333336</v>
-      </c>
-      <c r="H988" s="8">
-        <f t="shared" si="193"/>
-        <v>2257090</v>
-      </c>
-      <c r="I988" s="9">
-        <v>25</v>
-      </c>
-      <c r="L988" s="2">
-        <f t="shared" si="194"/>
-        <v>2257090</v>
-      </c>
-      <c r="M988" s="2">
-        <f t="shared" si="195"/>
-        <v>1336</v>
-      </c>
-      <c r="N988" s="15">
-        <f t="shared" si="196"/>
         <v>24724.255708830398</v>
       </c>
       <c r="O988" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41417.930004256777</v>
       </c>
       <c r="P988" s="16">
         <f>SUM($H$3:H988)</f>
-        <v>475872900</v>
+        <v>842873700</v>
       </c>
       <c r="Q988" s="2">
         <f>SUM($I$3:I988)</f>
-        <v>14924</v>
+        <v>34064</v>
       </c>
     </row>
     <row r="989" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A989" s="7">
+        <f t="shared" si="193"/>
+        <v>987</v>
+      </c>
+      <c r="B989" s="2">
+        <f t="shared" si="193"/>
+        <v>1337</v>
+      </c>
+      <c r="C989" s="14">
+        <f t="shared" si="191"/>
+        <v>24766.461722238088</v>
+      </c>
+      <c r="D989" s="14">
         <f t="shared" si="192"/>
-        <v>987</v>
-      </c>
-      <c r="B989" s="2">
-        <f t="shared" si="192"/>
-        <v>1337</v>
-      </c>
-      <c r="C989" s="14">
-        <f t="shared" si="190"/>
-        <v>24766.461722238088</v>
-      </c>
-      <c r="D989" s="14">
-        <f t="shared" si="191"/>
         <v>41495.33608910015</v>
       </c>
       <c r="E989" s="2">
         <v>1</v>
       </c>
       <c r="F989" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G989" s="17">
+        <f t="shared" si="190"/>
+        <v>0.3943666666666667</v>
+      </c>
+      <c r="H989" s="8">
+        <f t="shared" si="194"/>
+        <v>10051560</v>
+      </c>
+      <c r="I989" s="9">
+        <f t="shared" si="195"/>
+        <v>465</v>
+      </c>
+      <c r="L989" s="2">
+        <f t="shared" si="196"/>
+        <v>10051560</v>
+      </c>
+      <c r="M989" s="2">
+        <f t="shared" si="197"/>
+        <v>1337</v>
+      </c>
+      <c r="N989" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G989" s="17">
-        <f t="shared" si="189"/>
-        <v>0.3943666666666667</v>
-      </c>
-      <c r="H989" s="8">
-        <f t="shared" si="193"/>
-        <v>2269160</v>
-      </c>
-      <c r="I989" s="9">
-        <v>25</v>
-      </c>
-      <c r="L989" s="2">
-        <f t="shared" si="194"/>
-        <v>2269160</v>
-      </c>
-      <c r="M989" s="2">
-        <f t="shared" si="195"/>
-        <v>1337</v>
-      </c>
-      <c r="N989" s="15">
-        <f t="shared" si="196"/>
         <v>24766.461722238088</v>
       </c>
       <c r="O989" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41495.33608910015</v>
       </c>
       <c r="P989" s="16">
         <f>SUM($H$3:H989)</f>
-        <v>478142060</v>
+        <v>852925260</v>
       </c>
       <c r="Q989" s="2">
         <f>SUM($I$3:I989)</f>
-        <v>14949</v>
+        <v>34529</v>
       </c>
     </row>
     <row r="990" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A990" s="7">
+        <f t="shared" si="193"/>
+        <v>988</v>
+      </c>
+      <c r="B990" s="2">
+        <f t="shared" si="193"/>
+        <v>1338</v>
+      </c>
+      <c r="C990" s="14">
+        <f t="shared" si="191"/>
+        <v>24808.680024487381</v>
+      </c>
+      <c r="D990" s="14">
         <f t="shared" si="192"/>
-        <v>988</v>
-      </c>
-      <c r="B990" s="2">
-        <f t="shared" si="192"/>
-        <v>1338</v>
-      </c>
-      <c r="C990" s="14">
-        <f t="shared" si="190"/>
-        <v>24808.680024487381</v>
-      </c>
-      <c r="D990" s="14">
-        <f t="shared" si="191"/>
         <v>41572.787256124393</v>
       </c>
       <c r="E990" s="2">
         <v>1</v>
       </c>
       <c r="F990" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G990" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39479999999999998</v>
+      </c>
+      <c r="H990" s="8">
+        <f t="shared" si="194"/>
+        <v>10144630</v>
+      </c>
+      <c r="I990" s="9">
+        <f t="shared" si="195"/>
+        <v>470</v>
+      </c>
+      <c r="L990" s="2">
+        <f t="shared" si="196"/>
+        <v>10144630</v>
+      </c>
+      <c r="M990" s="2">
+        <f t="shared" si="197"/>
+        <v>1338</v>
+      </c>
+      <c r="N990" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G990" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39479999999999998</v>
-      </c>
-      <c r="H990" s="8">
-        <f t="shared" si="193"/>
-        <v>2281230</v>
-      </c>
-      <c r="I990" s="9">
-        <v>25</v>
-      </c>
-      <c r="L990" s="2">
-        <f t="shared" si="194"/>
-        <v>2281230</v>
-      </c>
-      <c r="M990" s="2">
-        <f t="shared" si="195"/>
-        <v>1338</v>
-      </c>
-      <c r="N990" s="15">
-        <f t="shared" si="196"/>
         <v>24808.680024487381</v>
       </c>
       <c r="O990" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41572.787256124393</v>
       </c>
       <c r="P990" s="16">
         <f>SUM($H$3:H990)</f>
-        <v>480423290</v>
+        <v>863069890</v>
       </c>
       <c r="Q990" s="2">
         <f>SUM($I$3:I990)</f>
-        <v>14974</v>
+        <v>34999</v>
       </c>
     </row>
     <row r="991" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A991" s="7">
+        <f t="shared" si="193"/>
+        <v>989</v>
+      </c>
+      <c r="B991" s="2">
+        <f t="shared" si="193"/>
+        <v>1339</v>
+      </c>
+      <c r="C991" s="14">
+        <f t="shared" si="191"/>
+        <v>24850.910601286872</v>
+      </c>
+      <c r="D991" s="14">
         <f t="shared" si="192"/>
-        <v>989</v>
-      </c>
-      <c r="B991" s="2">
-        <f t="shared" si="192"/>
-        <v>1339</v>
-      </c>
-      <c r="C991" s="14">
-        <f t="shared" si="190"/>
-        <v>24850.910601286872</v>
-      </c>
-      <c r="D991" s="14">
-        <f t="shared" si="191"/>
         <v>41650.28346600222</v>
       </c>
       <c r="E991" s="2">
         <v>1</v>
       </c>
       <c r="F991" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G991" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39523333333333338</v>
+      </c>
+      <c r="H991" s="8">
+        <f t="shared" si="194"/>
+        <v>10237700</v>
+      </c>
+      <c r="I991" s="9">
+        <f t="shared" si="195"/>
+        <v>475</v>
+      </c>
+      <c r="L991" s="2">
+        <f t="shared" si="196"/>
+        <v>10237700</v>
+      </c>
+      <c r="M991" s="2">
+        <f t="shared" si="197"/>
+        <v>1339</v>
+      </c>
+      <c r="N991" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G991" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39523333333333338</v>
-      </c>
-      <c r="H991" s="8">
-        <f t="shared" si="193"/>
-        <v>2293300</v>
-      </c>
-      <c r="I991" s="9">
-        <v>25</v>
-      </c>
-      <c r="L991" s="2">
-        <f t="shared" si="194"/>
-        <v>2293300</v>
-      </c>
-      <c r="M991" s="2">
-        <f t="shared" si="195"/>
-        <v>1339</v>
-      </c>
-      <c r="N991" s="15">
-        <f t="shared" si="196"/>
         <v>24850.910601286872</v>
       </c>
       <c r="O991" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41650.28346600222</v>
       </c>
       <c r="P991" s="16">
         <f>SUM($H$3:H991)</f>
-        <v>482716590</v>
+        <v>873307590</v>
       </c>
       <c r="Q991" s="2">
         <f>SUM($I$3:I991)</f>
-        <v>14999</v>
+        <v>35474</v>
       </c>
     </row>
     <row r="992" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A992" s="7">
+        <f t="shared" si="193"/>
+        <v>990</v>
+      </c>
+      <c r="B992" s="2">
+        <f t="shared" si="193"/>
+        <v>1340</v>
+      </c>
+      <c r="C992" s="14">
+        <f t="shared" si="191"/>
+        <v>24893.153438382396</v>
+      </c>
+      <c r="D992" s="14">
         <f t="shared" si="192"/>
-        <v>990</v>
-      </c>
-      <c r="B992" s="2">
-        <f t="shared" si="192"/>
-        <v>1340</v>
-      </c>
-      <c r="C992" s="14">
-        <f t="shared" si="190"/>
-        <v>24893.153438382396</v>
-      </c>
-      <c r="D992" s="14">
-        <f t="shared" si="191"/>
         <v>41727.824679497535</v>
       </c>
       <c r="E992" s="2">
         <v>1</v>
       </c>
       <c r="F992" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G992" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39566666666666672</v>
+      </c>
+      <c r="H992" s="8">
+        <f t="shared" si="194"/>
+        <v>10330770</v>
+      </c>
+      <c r="I992" s="9">
+        <f t="shared" si="195"/>
+        <v>480</v>
+      </c>
+      <c r="L992" s="2">
+        <f t="shared" si="196"/>
+        <v>10330770</v>
+      </c>
+      <c r="M992" s="2">
+        <f t="shared" si="197"/>
+        <v>1340</v>
+      </c>
+      <c r="N992" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G992" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39566666666666672</v>
-      </c>
-      <c r="H992" s="8">
-        <f t="shared" si="193"/>
-        <v>2305370</v>
-      </c>
-      <c r="I992" s="9">
-        <v>25</v>
-      </c>
-      <c r="L992" s="2">
-        <f t="shared" si="194"/>
-        <v>2305370</v>
-      </c>
-      <c r="M992" s="2">
-        <f t="shared" si="195"/>
-        <v>1340</v>
-      </c>
-      <c r="N992" s="15">
-        <f t="shared" si="196"/>
         <v>24893.153438382396</v>
       </c>
       <c r="O992" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41727.824679497535</v>
       </c>
       <c r="P992" s="16">
         <f>SUM($H$3:H992)</f>
-        <v>485021960</v>
+        <v>883638360</v>
       </c>
       <c r="Q992" s="2">
         <f>SUM($I$3:I992)</f>
-        <v>15024</v>
+        <v>35954</v>
       </c>
     </row>
     <row r="993" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A993" s="7">
+        <f t="shared" si="193"/>
+        <v>991</v>
+      </c>
+      <c r="B993" s="2">
+        <f t="shared" si="193"/>
+        <v>1341</v>
+      </c>
+      <c r="C993" s="14">
+        <f t="shared" si="191"/>
+        <v>24935.408521557161</v>
+      </c>
+      <c r="D993" s="14">
         <f t="shared" si="192"/>
-        <v>991</v>
-      </c>
-      <c r="B993" s="2">
-        <f t="shared" si="192"/>
-        <v>1341</v>
-      </c>
-      <c r="C993" s="14">
-        <f t="shared" si="190"/>
-        <v>24935.408521557161</v>
-      </c>
-      <c r="D993" s="14">
-        <f t="shared" si="191"/>
         <v>41805.410857465562</v>
       </c>
       <c r="E993" s="2">
         <v>1</v>
       </c>
       <c r="F993" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G993" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39610000000000001</v>
+      </c>
+      <c r="H993" s="8">
+        <f t="shared" si="194"/>
+        <v>10423840</v>
+      </c>
+      <c r="I993" s="9">
+        <f t="shared" si="195"/>
+        <v>485</v>
+      </c>
+      <c r="L993" s="2">
+        <f t="shared" si="196"/>
+        <v>10423840</v>
+      </c>
+      <c r="M993" s="2">
+        <f t="shared" si="197"/>
+        <v>1341</v>
+      </c>
+      <c r="N993" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G993" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39610000000000001</v>
-      </c>
-      <c r="H993" s="8">
-        <f t="shared" si="193"/>
-        <v>2317440</v>
-      </c>
-      <c r="I993" s="9">
-        <v>25</v>
-      </c>
-      <c r="L993" s="2">
-        <f t="shared" si="194"/>
-        <v>2317440</v>
-      </c>
-      <c r="M993" s="2">
-        <f t="shared" si="195"/>
-        <v>1341</v>
-      </c>
-      <c r="N993" s="15">
-        <f t="shared" si="196"/>
         <v>24935.408521557161</v>
       </c>
       <c r="O993" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41805.410857465562</v>
       </c>
       <c r="P993" s="16">
         <f>SUM($H$3:H993)</f>
-        <v>487339400</v>
+        <v>894062200</v>
       </c>
       <c r="Q993" s="2">
         <f>SUM($I$3:I993)</f>
-        <v>15049</v>
+        <v>36439</v>
       </c>
     </row>
     <row r="994" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A994" s="7">
+        <f t="shared" si="193"/>
+        <v>992</v>
+      </c>
+      <c r="B994" s="2">
+        <f t="shared" si="193"/>
+        <v>1342</v>
+      </c>
+      <c r="C994" s="14">
+        <f t="shared" si="191"/>
+        <v>24977.675836631173</v>
+      </c>
+      <c r="D994" s="14">
         <f t="shared" si="192"/>
-        <v>992</v>
-      </c>
-      <c r="B994" s="2">
-        <f t="shared" si="192"/>
-        <v>1342</v>
-      </c>
-      <c r="C994" s="14">
-        <f t="shared" si="190"/>
-        <v>24977.675836631173</v>
-      </c>
-      <c r="D994" s="14">
-        <f t="shared" si="191"/>
         <v>41883.04196085182</v>
       </c>
       <c r="E994" s="2">
         <v>1</v>
       </c>
       <c r="F994" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G994" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39653333333333335</v>
+      </c>
+      <c r="H994" s="8">
+        <f t="shared" si="194"/>
+        <v>10516910</v>
+      </c>
+      <c r="I994" s="9">
+        <f t="shared" si="195"/>
+        <v>490</v>
+      </c>
+      <c r="L994" s="2">
+        <f t="shared" si="196"/>
+        <v>10516910</v>
+      </c>
+      <c r="M994" s="2">
+        <f t="shared" si="197"/>
+        <v>1342</v>
+      </c>
+      <c r="N994" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G994" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39653333333333335</v>
-      </c>
-      <c r="H994" s="8">
-        <f t="shared" si="193"/>
-        <v>2329510</v>
-      </c>
-      <c r="I994" s="9">
-        <v>25</v>
-      </c>
-      <c r="L994" s="2">
-        <f t="shared" si="194"/>
-        <v>2329510</v>
-      </c>
-      <c r="M994" s="2">
-        <f t="shared" si="195"/>
-        <v>1342</v>
-      </c>
-      <c r="N994" s="15">
-        <f t="shared" si="196"/>
         <v>24977.675836631173</v>
       </c>
       <c r="O994" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41883.04196085182</v>
       </c>
       <c r="P994" s="16">
         <f>SUM($H$3:H994)</f>
-        <v>489668910</v>
+        <v>904579110</v>
       </c>
       <c r="Q994" s="2">
         <f>SUM($I$3:I994)</f>
-        <v>15074</v>
+        <v>36929</v>
       </c>
     </row>
     <row r="995" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A995" s="7">
+        <f t="shared" si="193"/>
+        <v>993</v>
+      </c>
+      <c r="B995" s="2">
+        <f t="shared" si="193"/>
+        <v>1343</v>
+      </c>
+      <c r="C995" s="14">
+        <f t="shared" si="191"/>
+        <v>25019.955369461553</v>
+      </c>
+      <c r="D995" s="14">
         <f t="shared" si="192"/>
-        <v>993</v>
-      </c>
-      <c r="B995" s="2">
-        <f t="shared" si="192"/>
-        <v>1343</v>
-      </c>
-      <c r="C995" s="14">
-        <f t="shared" si="190"/>
-        <v>25019.955369461553</v>
-      </c>
-      <c r="D995" s="14">
-        <f t="shared" si="191"/>
         <v>41960.717950692502</v>
       </c>
       <c r="E995" s="2">
         <v>1</v>
       </c>
       <c r="F995" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G995" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39696666666666675</v>
+      </c>
+      <c r="H995" s="8">
+        <f t="shared" si="194"/>
+        <v>10609980</v>
+      </c>
+      <c r="I995" s="9">
+        <f t="shared" si="195"/>
+        <v>495</v>
+      </c>
+      <c r="L995" s="2">
+        <f t="shared" si="196"/>
+        <v>10609980</v>
+      </c>
+      <c r="M995" s="2">
+        <f t="shared" si="197"/>
+        <v>1343</v>
+      </c>
+      <c r="N995" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G995" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39696666666666675</v>
-      </c>
-      <c r="H995" s="8">
-        <f t="shared" si="193"/>
-        <v>2341580</v>
-      </c>
-      <c r="I995" s="9">
-        <v>25</v>
-      </c>
-      <c r="L995" s="2">
-        <f t="shared" si="194"/>
-        <v>2341580</v>
-      </c>
-      <c r="M995" s="2">
-        <f t="shared" si="195"/>
-        <v>1343</v>
-      </c>
-      <c r="N995" s="15">
-        <f t="shared" si="196"/>
         <v>25019.955369461553</v>
       </c>
       <c r="O995" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>41960.717950692502</v>
       </c>
       <c r="P995" s="16">
         <f>SUM($H$3:H995)</f>
-        <v>492010490</v>
+        <v>915189090</v>
       </c>
       <c r="Q995" s="2">
         <f>SUM($I$3:I995)</f>
-        <v>15099</v>
+        <v>37424</v>
       </c>
     </row>
     <row r="996" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A996" s="7">
+        <f t="shared" si="193"/>
+        <v>994</v>
+      </c>
+      <c r="B996" s="2">
+        <f t="shared" si="193"/>
+        <v>1344</v>
+      </c>
+      <c r="C996" s="14">
+        <f t="shared" si="191"/>
+        <v>25062.24710594201</v>
+      </c>
+      <c r="D996" s="14">
         <f t="shared" si="192"/>
-        <v>994</v>
-      </c>
-      <c r="B996" s="2">
-        <f t="shared" si="192"/>
-        <v>1344</v>
-      </c>
-      <c r="C996" s="14">
-        <f t="shared" si="190"/>
-        <v>25062.24710594201</v>
-      </c>
-      <c r="D996" s="14">
-        <f t="shared" si="191"/>
         <v>42038.438788113606</v>
       </c>
       <c r="E996" s="2">
         <v>1</v>
       </c>
       <c r="F996" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G996" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39740000000000003</v>
+      </c>
+      <c r="H996" s="8">
+        <f t="shared" si="194"/>
+        <v>10703050</v>
+      </c>
+      <c r="I996" s="9">
+        <f t="shared" si="195"/>
+        <v>500</v>
+      </c>
+      <c r="L996" s="2">
+        <f t="shared" si="196"/>
+        <v>10703050</v>
+      </c>
+      <c r="M996" s="2">
+        <f t="shared" si="197"/>
+        <v>1344</v>
+      </c>
+      <c r="N996" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G996" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39740000000000003</v>
-      </c>
-      <c r="H996" s="8">
-        <f t="shared" si="193"/>
-        <v>2353650</v>
-      </c>
-      <c r="I996" s="9">
-        <v>25</v>
-      </c>
-      <c r="L996" s="2">
-        <f t="shared" si="194"/>
-        <v>2353650</v>
-      </c>
-      <c r="M996" s="2">
-        <f t="shared" si="195"/>
-        <v>1344</v>
-      </c>
-      <c r="N996" s="15">
-        <f t="shared" si="196"/>
         <v>25062.24710594201</v>
       </c>
       <c r="O996" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>42038.438788113606</v>
       </c>
       <c r="P996" s="16">
         <f>SUM($H$3:H996)</f>
-        <v>494364140</v>
+        <v>925892140</v>
       </c>
       <c r="Q996" s="2">
         <f>SUM($I$3:I996)</f>
-        <v>15124</v>
+        <v>37924</v>
       </c>
     </row>
     <row r="997" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A997" s="7">
+        <f t="shared" si="193"/>
+        <v>995</v>
+      </c>
+      <c r="B997" s="2">
+        <f t="shared" si="193"/>
+        <v>1345</v>
+      </c>
+      <c r="C997" s="14">
+        <f t="shared" si="191"/>
+        <v>25104.551032002899</v>
+      </c>
+      <c r="D997" s="14">
         <f t="shared" si="192"/>
-        <v>995</v>
-      </c>
-      <c r="B997" s="2">
-        <f t="shared" si="192"/>
-        <v>1345</v>
-      </c>
-      <c r="C997" s="14">
-        <f t="shared" si="190"/>
-        <v>25104.551032002899</v>
-      </c>
-      <c r="D997" s="14">
-        <f t="shared" si="191"/>
         <v>42116.204434330801</v>
       </c>
       <c r="E997" s="2">
         <v>1</v>
       </c>
       <c r="F997" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G997" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39783333333333337</v>
+      </c>
+      <c r="H997" s="8">
+        <f t="shared" si="194"/>
+        <v>10796120</v>
+      </c>
+      <c r="I997" s="9">
+        <f t="shared" si="195"/>
+        <v>505</v>
+      </c>
+      <c r="L997" s="2">
+        <f t="shared" si="196"/>
+        <v>10796120</v>
+      </c>
+      <c r="M997" s="2">
+        <f t="shared" si="197"/>
+        <v>1345</v>
+      </c>
+      <c r="N997" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G997" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39783333333333337</v>
-      </c>
-      <c r="H997" s="8">
-        <f t="shared" si="193"/>
-        <v>2365720</v>
-      </c>
-      <c r="I997" s="9">
-        <v>25</v>
-      </c>
-      <c r="L997" s="2">
-        <f t="shared" si="194"/>
-        <v>2365720</v>
-      </c>
-      <c r="M997" s="2">
-        <f t="shared" si="195"/>
-        <v>1345</v>
-      </c>
-      <c r="N997" s="15">
-        <f t="shared" si="196"/>
         <v>25104.551032002899</v>
       </c>
       <c r="O997" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>42116.204434330801</v>
       </c>
       <c r="P997" s="16">
         <f>SUM($H$3:H997)</f>
-        <v>496729860</v>
+        <v>936688260</v>
       </c>
       <c r="Q997" s="2">
         <f>SUM($I$3:I997)</f>
-        <v>15149</v>
+        <v>38429</v>
       </c>
     </row>
     <row r="998" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A998" s="7">
+        <f t="shared" si="193"/>
+        <v>996</v>
+      </c>
+      <c r="B998" s="2">
+        <f t="shared" si="193"/>
+        <v>1346</v>
+      </c>
+      <c r="C998" s="14">
+        <f t="shared" si="191"/>
+        <v>25146.867133611056</v>
+      </c>
+      <c r="D998" s="14">
         <f t="shared" si="192"/>
-        <v>996</v>
-      </c>
-      <c r="B998" s="2">
-        <f t="shared" si="192"/>
-        <v>1346</v>
-      </c>
-      <c r="C998" s="14">
-        <f t="shared" si="190"/>
-        <v>25146.867133611056</v>
-      </c>
-      <c r="D998" s="14">
-        <f t="shared" si="191"/>
         <v>42194.014850649008</v>
       </c>
       <c r="E998" s="2">
         <v>1</v>
       </c>
       <c r="F998" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G998" s="17">
+        <f t="shared" si="190"/>
+        <v>0.39826666666666666</v>
+      </c>
+      <c r="H998" s="8">
+        <f t="shared" si="194"/>
+        <v>10889190</v>
+      </c>
+      <c r="I998" s="9">
+        <f t="shared" si="195"/>
+        <v>510</v>
+      </c>
+      <c r="L998" s="2">
+        <f t="shared" si="196"/>
+        <v>10889190</v>
+      </c>
+      <c r="M998" s="2">
+        <f t="shared" si="197"/>
+        <v>1346</v>
+      </c>
+      <c r="N998" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G998" s="17">
-        <f t="shared" si="189"/>
-        <v>0.39826666666666666</v>
-      </c>
-      <c r="H998" s="8">
-        <f t="shared" si="193"/>
-        <v>2377790</v>
-      </c>
-      <c r="I998" s="9">
-        <v>25</v>
-      </c>
-      <c r="L998" s="2">
-        <f t="shared" si="194"/>
-        <v>2377790</v>
-      </c>
-      <c r="M998" s="2">
-        <f t="shared" si="195"/>
-        <v>1346</v>
-      </c>
-      <c r="N998" s="15">
-        <f t="shared" si="196"/>
         <v>25146.867133611056</v>
       </c>
       <c r="O998" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>42194.014850649008</v>
       </c>
       <c r="P998" s="16">
         <f>SUM($H$3:H998)</f>
-        <v>499107650</v>
+        <v>947577450</v>
       </c>
       <c r="Q998" s="2">
         <f>SUM($I$3:I998)</f>
-        <v>15174</v>
+        <v>38939</v>
       </c>
     </row>
     <row r="999" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A999" s="7">
+        <f t="shared" si="193"/>
+        <v>997</v>
+      </c>
+      <c r="B999" s="2">
+        <f t="shared" si="193"/>
+        <v>1347</v>
+      </c>
+      <c r="C999" s="14">
+        <f t="shared" si="191"/>
+        <v>25189.195396769548</v>
+      </c>
+      <c r="D999" s="14">
         <f t="shared" si="192"/>
-        <v>997</v>
-      </c>
-      <c r="B999" s="2">
-        <f t="shared" si="192"/>
-        <v>1347</v>
-      </c>
-      <c r="C999" s="14">
-        <f t="shared" si="190"/>
-        <v>25189.195396769548</v>
-      </c>
-      <c r="D999" s="14">
-        <f t="shared" si="191"/>
         <v>42271.869998462258</v>
       </c>
       <c r="E999" s="2">
         <v>1</v>
       </c>
       <c r="F999" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G999" s="17">
+        <f t="shared" ref="G999:G1002" si="201">0.01 + (A999-100)*(0.4-0.01)/(1000-100)</f>
+        <v>0.3987</v>
+      </c>
+      <c r="H999" s="8">
+        <f t="shared" si="194"/>
+        <v>10982260</v>
+      </c>
+      <c r="I999" s="9">
+        <f t="shared" si="195"/>
+        <v>515</v>
+      </c>
+      <c r="L999" s="2">
+        <f t="shared" si="196"/>
+        <v>10982260</v>
+      </c>
+      <c r="M999" s="2">
+        <f t="shared" si="197"/>
+        <v>1347</v>
+      </c>
+      <c r="N999" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G999" s="17">
-        <f t="shared" ref="G999:G1002" si="199">0.01 + (A999-100)*(0.4-0.01)/(1000-100)</f>
-        <v>0.3987</v>
-      </c>
-      <c r="H999" s="8">
-        <f t="shared" si="193"/>
-        <v>2389860</v>
-      </c>
-      <c r="I999" s="9">
-        <v>25</v>
-      </c>
-      <c r="L999" s="2">
-        <f t="shared" si="194"/>
-        <v>2389860</v>
-      </c>
-      <c r="M999" s="2">
-        <f t="shared" si="195"/>
-        <v>1347</v>
-      </c>
-      <c r="N999" s="15">
-        <f t="shared" si="196"/>
         <v>25189.195396769548</v>
       </c>
       <c r="O999" s="15">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>42271.869998462258</v>
       </c>
       <c r="P999" s="16">
         <f>SUM($H$3:H999)</f>
-        <v>501497510</v>
+        <v>958559710</v>
       </c>
       <c r="Q999" s="2">
         <f>SUM($I$3:I999)</f>
-        <v>15199</v>
+        <v>39454</v>
       </c>
     </row>
     <row r="1000" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1000" s="7">
+        <f t="shared" si="193"/>
+        <v>998</v>
+      </c>
+      <c r="B1000" s="2">
+        <f t="shared" si="193"/>
+        <v>1348</v>
+      </c>
+      <c r="C1000" s="14">
+        <f t="shared" si="191"/>
+        <v>25231.535807517641</v>
+      </c>
+      <c r="D1000" s="14">
         <f t="shared" si="192"/>
-        <v>998</v>
-      </c>
-      <c r="B1000" s="2">
-        <f t="shared" si="192"/>
-        <v>1348</v>
-      </c>
-      <c r="C1000" s="14">
-        <f t="shared" si="190"/>
-        <v>25231.535807517641</v>
-      </c>
-      <c r="D1000" s="14">
-        <f t="shared" si="191"/>
         <v>42349.769839253189</v>
       </c>
       <c r="E1000" s="2">
         <v>1</v>
       </c>
       <c r="F1000" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G1000" s="17">
+        <f t="shared" si="201"/>
+        <v>0.3991333333333334</v>
+      </c>
+      <c r="H1000" s="8">
+        <f t="shared" si="194"/>
+        <v>11075330</v>
+      </c>
+      <c r="I1000" s="9">
+        <f t="shared" si="195"/>
+        <v>520</v>
+      </c>
+      <c r="L1000" s="2">
+        <f t="shared" si="196"/>
+        <v>11075330</v>
+      </c>
+      <c r="M1000" s="2">
+        <f t="shared" si="197"/>
+        <v>1348</v>
+      </c>
+      <c r="N1000" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G1000" s="17">
+        <v>25231.535807517641</v>
+      </c>
+      <c r="O1000" s="15">
         <f t="shared" si="199"/>
-        <v>0.3991333333333334</v>
-      </c>
-      <c r="H1000" s="8">
-        <f t="shared" si="193"/>
-        <v>2401930</v>
-      </c>
-      <c r="I1000" s="9">
-        <v>25</v>
-      </c>
-      <c r="L1000" s="2">
-        <f t="shared" si="194"/>
-        <v>2401930</v>
-      </c>
-      <c r="M1000" s="2">
-        <f t="shared" si="195"/>
-        <v>1348</v>
-      </c>
-      <c r="N1000" s="15">
-        <f t="shared" si="196"/>
-        <v>25231.535807517641</v>
-      </c>
-      <c r="O1000" s="15">
-        <f t="shared" si="197"/>
         <v>42349.769839253189</v>
       </c>
       <c r="P1000" s="16">
         <f>SUM($H$3:H1000)</f>
-        <v>503899440</v>
+        <v>969635040</v>
       </c>
       <c r="Q1000" s="2">
         <f>SUM($I$3:I1000)</f>
-        <v>15224</v>
+        <v>39974</v>
       </c>
     </row>
     <row r="1001" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1001" s="7">
+        <f t="shared" si="193"/>
+        <v>999</v>
+      </c>
+      <c r="B1001" s="2">
+        <f t="shared" si="193"/>
+        <v>1349</v>
+      </c>
+      <c r="C1001" s="14">
+        <f t="shared" si="191"/>
+        <v>25273.888351930589</v>
+      </c>
+      <c r="D1001" s="14">
         <f t="shared" si="192"/>
-        <v>999</v>
-      </c>
-      <c r="B1001" s="2">
-        <f t="shared" si="192"/>
-        <v>1349</v>
-      </c>
-      <c r="C1001" s="14">
-        <f t="shared" si="190"/>
-        <v>25273.888351930589</v>
-      </c>
-      <c r="D1001" s="14">
-        <f t="shared" si="191"/>
         <v>42427.714334592667</v>
       </c>
       <c r="E1001" s="2">
         <v>1</v>
       </c>
       <c r="F1001" s="2">
+        <f t="shared" si="200"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G1001" s="17">
+        <f t="shared" si="201"/>
+        <v>0.39956666666666668</v>
+      </c>
+      <c r="H1001" s="8">
+        <f t="shared" si="194"/>
+        <v>11168400</v>
+      </c>
+      <c r="I1001" s="9">
+        <f t="shared" si="195"/>
+        <v>525</v>
+      </c>
+      <c r="L1001" s="2">
+        <f t="shared" si="196"/>
+        <v>11168400</v>
+      </c>
+      <c r="M1001" s="2">
+        <f t="shared" si="197"/>
+        <v>1349</v>
+      </c>
+      <c r="N1001" s="15">
         <f t="shared" si="198"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="G1001" s="17">
+        <v>25273.888351930589</v>
+      </c>
+      <c r="O1001" s="15">
         <f t="shared" si="199"/>
-        <v>0.39956666666666668</v>
-      </c>
-      <c r="H1001" s="8">
-        <f t="shared" si="193"/>
-        <v>2414000</v>
-      </c>
-      <c r="I1001" s="9">
-        <v>25</v>
-      </c>
-      <c r="L1001" s="2">
-        <f t="shared" si="194"/>
-        <v>2414000</v>
-      </c>
-      <c r="M1001" s="2">
-        <f t="shared" si="195"/>
-        <v>1349</v>
-      </c>
-      <c r="N1001" s="15">
-        <f t="shared" si="196"/>
-        <v>25273.888351930589</v>
-      </c>
-      <c r="O1001" s="15">
-        <f t="shared" si="197"/>
         <v>42427.714334592667</v>
       </c>
       <c r="P1001" s="16">
         <f>SUM($H$3:H1001)</f>
-        <v>506313440</v>
+        <v>980803440</v>
       </c>
       <c r="Q1001" s="2">
         <f>SUM($I$3:I1001)</f>
-        <v>15249</v>
+        <v>40499</v>
       </c>
     </row>
     <row r="1002" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1002" s="7">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>1000</v>
       </c>
       <c r="B1002" s="2">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>1350</v>
       </c>
       <c r="C1002" s="2">
@@ -61224,43 +61324,44 @@
         <v>1</v>
       </c>
       <c r="F1002" s="2">
+        <f t="shared" si="200"/>
+        <v>9.3999999999999986</v>
+      </c>
+      <c r="G1002" s="17">
+        <f t="shared" si="201"/>
+        <v>0.4</v>
+      </c>
+      <c r="H1002" s="8">
+        <f t="shared" si="194"/>
+        <v>11261470</v>
+      </c>
+      <c r="I1002" s="9">
+        <f t="shared" si="195"/>
+        <v>530</v>
+      </c>
+      <c r="L1002" s="2">
+        <f t="shared" si="196"/>
+        <v>11261470</v>
+      </c>
+      <c r="M1002" s="2">
+        <f t="shared" si="197"/>
+        <v>1350</v>
+      </c>
+      <c r="N1002" s="15">
         <f t="shared" si="198"/>
-        <v>9.3999999999999986</v>
-      </c>
-      <c r="G1002" s="17">
+        <v>25500</v>
+      </c>
+      <c r="O1002" s="15">
         <f t="shared" si="199"/>
-        <v>0.4</v>
-      </c>
-      <c r="H1002" s="8">
-        <f t="shared" si="193"/>
-        <v>2426070</v>
-      </c>
-      <c r="I1002" s="9">
-        <v>25</v>
-      </c>
-      <c r="L1002" s="2">
-        <f t="shared" si="194"/>
-        <v>2426070</v>
-      </c>
-      <c r="M1002" s="2">
-        <f t="shared" si="195"/>
-        <v>1350</v>
-      </c>
-      <c r="N1002" s="15">
-        <f t="shared" si="196"/>
-        <v>25500</v>
-      </c>
-      <c r="O1002" s="15">
-        <f t="shared" si="197"/>
         <v>43000</v>
       </c>
       <c r="P1002" s="16">
         <f>SUM($H$3:H1002)</f>
-        <v>508739510</v>
+        <v>992064910</v>
       </c>
       <c r="Q1002" s="2">
         <f>SUM($I$3:I1002)</f>
-        <v>15274</v>
+        <v>41029</v>
       </c>
     </row>
     <row r="1003" spans="1:17" x14ac:dyDescent="0.3">
@@ -61292,7 +61393,7 @@
         <v>-1</v>
       </c>
       <c r="L1003" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>-1</v>
       </c>
       <c r="N1003" s="15"/>
